--- a/database/event/3425/event_3425_evp_summary.xlsx
+++ b/database/event/3425/event_3425_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>0.7612</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4997</v>
+        <v>2.4368</v>
       </c>
       <c r="E2" t="n">
         <v>7.2307</v>
@@ -548,7 +548,7 @@
         <v>0.7131</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3153</v>
+        <v>2.255</v>
       </c>
       <c r="E3" t="n">
         <v>6.7744</v>
@@ -594,7 +594,7 @@
         <v>0.5476</v>
       </c>
       <c r="D4" t="n">
-        <v>1.68</v>
+        <v>1.6284</v>
       </c>
       <c r="E4" t="n">
         <v>5.2017</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mertz</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7015</v>
+        <v>5.002</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4949</v>
+        <v>0.5266</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4779</v>
+        <v>1.5489</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7015</v>
+        <v>5.002</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9206</v>
+        <v>2.1243</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7809</v>
+        <v>2.8777</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9206</v>
+        <v>2.1243</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5567</v>
+        <v>1.7218</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7809</v>
+        <v>2.8777</v>
       </c>
       <c r="K5" t="n">
         <v>54</v>
@@ -667,7 +667,7 @@
         <v>130</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3376</v>
+        <v>4.5995</v>
       </c>
       <c r="N5" t="n">
         <v>184</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>mertz</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6921</v>
+        <v>4.9168</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4939</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4741</v>
+        <v>1.5149</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6921</v>
+        <v>4.9168</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8144</v>
+        <v>2.1359</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8777</v>
+        <v>2.7809</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8144</v>
+        <v>2.1359</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4706</v>
+        <v>1.7312</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8777</v>
+        <v>2.7809</v>
       </c>
       <c r="K6" t="n">
         <v>54</v>
@@ -713,7 +713,7 @@
         <v>130</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3483</v>
+        <v>4.5121</v>
       </c>
       <c r="N6" t="n">
         <v>184</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.098</v>
+        <v>4.6091</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4314</v>
+        <v>0.4852</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2341</v>
+        <v>1.3924</v>
       </c>
       <c r="E7" t="n">
-        <v>4.098</v>
+        <v>4.6091</v>
       </c>
       <c r="F7" t="n">
-        <v>1.995</v>
+        <v>2.5061</v>
       </c>
       <c r="G7" t="n">
         <v>2.103</v>
       </c>
       <c r="H7" t="n">
-        <v>1.995</v>
+        <v>2.5061</v>
       </c>
       <c r="I7" t="n">
-        <v>1.617</v>
+        <v>2.0312</v>
       </c>
       <c r="J7" t="n">
         <v>2.103</v>
@@ -759,7 +759,7 @@
         <v>130</v>
       </c>
       <c r="M7" t="n">
-        <v>3.72</v>
+        <v>4.1342</v>
       </c>
       <c r="N7" t="n">
         <v>184</v>
@@ -778,7 +778,7 @@
         <v>0.4234</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2033</v>
+        <v>1.1583</v>
       </c>
       <c r="E8" t="n">
         <v>4.0217</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.6479</v>
+        <v>2.638</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2787</v>
+        <v>0.2777</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6483</v>
+        <v>0.6071</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6479</v>
+        <v>2.638</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6479</v>
+        <v>2.638</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6479</v>
+        <v>2.638</v>
       </c>
       <c r="I9" t="n">
         <v>2.6602</v>
@@ -860,81 +860,81 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3561</v>
+        <v>2.3672</v>
       </c>
       <c r="C10" t="n">
-        <v>0.248</v>
+        <v>0.2492</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5304</v>
+        <v>0.4992</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3561</v>
+        <v>2.3672</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5701</v>
+        <v>2.3672</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.214</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5701</v>
+        <v>2.3672</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0831</v>
+        <v>2.3672</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.214</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="L10" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8691</v>
+        <v>2.3672</v>
       </c>
       <c r="N10" t="n">
-        <v>226</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8192</v>
+        <v>2.3561</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1915</v>
+        <v>0.248</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3136</v>
+        <v>0.4948</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8192</v>
+        <v>2.3561</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8066</v>
+        <v>2.5701</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0126</v>
+        <v>-0.214</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8066</v>
+        <v>2.5701</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6536999999999999</v>
+        <v>2.0831</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0126</v>
+        <v>-0.214</v>
       </c>
       <c r="K11" t="n">
         <v>149</v>
@@ -943,7 +943,7 @@
         <v>77</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6663</v>
+        <v>1.8691</v>
       </c>
       <c r="N11" t="n">
         <v>226</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6948</v>
+        <v>2.009</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1784</v>
+        <v>0.2115</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2633</v>
+        <v>0.3565</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6948</v>
+        <v>2.009</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4971</v>
+        <v>0.9964</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8023</v>
+        <v>1.0126</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4971</v>
+        <v>0.9964</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0239</v>
+        <v>0.8076</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8023</v>
+        <v>1.0126</v>
       </c>
       <c r="K12" t="n">
         <v>149</v>
@@ -989,7 +989,7 @@
         <v>77</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2216</v>
+        <v>1.8202</v>
       </c>
       <c r="N12" t="n">
         <v>226</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6634</v>
+        <v>1.7584</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1751</v>
+        <v>0.1851</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2506</v>
+        <v>0.2566</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6634</v>
+        <v>1.7584</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1119</v>
+        <v>0.2069</v>
       </c>
       <c r="G13" t="n">
         <v>1.5515</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1119</v>
+        <v>0.2069</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0907</v>
+        <v>0.1677</v>
       </c>
       <c r="J13" t="n">
         <v>1.5515</v>
@@ -1035,7 +1035,7 @@
         <v>130</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6422</v>
+        <v>1.7192</v>
       </c>
       <c r="N13" t="n">
         <v>184</v>
@@ -1044,323 +1044,323 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4365</v>
+        <v>1.6948</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1512</v>
+        <v>0.1784</v>
       </c>
       <c r="D14" t="n">
-        <v>0.159</v>
+        <v>0.2313</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4365</v>
+        <v>1.6948</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4365</v>
+        <v>2.4971</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.8023</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4365</v>
+        <v>2.4971</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4365</v>
+        <v>2.0239</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.8023</v>
       </c>
       <c r="K14" t="n">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4365</v>
+        <v>1.2216</v>
       </c>
       <c r="N14" t="n">
-        <v>83</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GruBy</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3899</v>
+        <v>1.4327</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1463</v>
+        <v>0.1508</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1401</v>
+        <v>0.1269</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3899</v>
+        <v>1.4327</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3899</v>
+        <v>2.3096</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.8769</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3899</v>
+        <v>2.3096</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3964</v>
+        <v>1.872</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.8769</v>
       </c>
       <c r="K15" t="n">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3964</v>
+        <v>0.9951000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>162</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>GruBy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3436</v>
+        <v>1.3847</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1414</v>
+        <v>0.1458</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1214</v>
+        <v>0.1078</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3436</v>
+        <v>1.3847</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4142</v>
+        <v>1.3847</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9294</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4142</v>
+        <v>1.3847</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3357</v>
+        <v>1.3964</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9294</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="L16" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2651</v>
+        <v>1.3964</v>
       </c>
       <c r="N16" t="n">
-        <v>184</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>phr</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2896</v>
+        <v>1.3451</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1358</v>
+        <v>0.1416</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2896</v>
+        <v>1.3451</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2896</v>
+        <v>0.4157</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.9294</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2896</v>
+        <v>0.4157</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2956</v>
+        <v>0.3369</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.9294</v>
       </c>
       <c r="K17" t="n">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2956</v>
+        <v>1.2663</v>
       </c>
       <c r="N17" t="n">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1598</v>
+        <v>1.2876</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1221</v>
+        <v>0.1355</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0472</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1598</v>
+        <v>1.2876</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1598</v>
+        <v>2.1059</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.8183</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1598</v>
+        <v>2.1059</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1652</v>
+        <v>1.7069</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.8183</v>
       </c>
       <c r="K18" t="n">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1652</v>
+        <v>0.8886000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>162</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>phr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0507</v>
+        <v>1.2848</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1106</v>
+        <v>0.1352</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0031</v>
+        <v>0.068</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0507</v>
+        <v>1.2848</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9276</v>
+        <v>1.2848</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8769</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9276</v>
+        <v>1.2848</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5623</v>
+        <v>1.2956</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8769</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="L19" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6854</v>
+        <v>1.2956</v>
       </c>
       <c r="N19" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9381</v>
+        <v>1.1554</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0988</v>
+        <v>0.1216</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0424</v>
+        <v>0.0164</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9381</v>
+        <v>1.1554</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7564</v>
+        <v>1.1554</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8183</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7564</v>
+        <v>1.1554</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4236</v>
+        <v>1.1652</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8183</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="L20" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.1652</v>
       </c>
       <c r="N20" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21">
@@ -1376,7 +1376,7 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1789</v>
+        <v>-0.2048</v>
       </c>
       <c r="E21" t="n">
         <v>0.6002999999999999</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>disco doplan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5601</v>
+        <v>0.5828</v>
       </c>
       <c r="C22" t="n">
-        <v>0.059</v>
+        <v>0.0614</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1951</v>
+        <v>-0.2117</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5601</v>
+        <v>0.5828</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5601</v>
+        <v>1.5828</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5601</v>
+        <v>1.5828</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5601</v>
+        <v>1.2829</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K22" t="n">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5601</v>
+        <v>0.2828999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>disco doplan</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5576</v>
+        <v>0.5601</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0587</v>
+        <v>0.059</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1961</v>
+        <v>-0.2208</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5576</v>
+        <v>0.5601</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5576</v>
+        <v>0.5601</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5576</v>
+        <v>0.5601</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2625</v>
+        <v>0.5601</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="L23" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2625</v>
+        <v>0.5601</v>
       </c>
       <c r="N23" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
@@ -1514,7 +1514,7 @@
         <v>0.0574</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.201</v>
+        <v>-0.2266</v>
       </c>
       <c r="E24" t="n">
         <v>0.5454</v>
@@ -1550,216 +1550,216 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nukkye</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.06</v>
+        <v>0.2062</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0063</v>
+        <v>0.0217</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3971</v>
+        <v>-0.3618</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06</v>
+        <v>0.2062</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06</v>
+        <v>0.2062</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.06</v>
+        <v>0.2062</v>
       </c>
       <c r="I25" t="n">
-        <v>0.06</v>
+        <v>0.2062</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.06</v>
+        <v>0.2062</v>
       </c>
       <c r="N25" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AZK</t>
+          <t>nukkye</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0195</v>
+        <v>0.06</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0021</v>
+        <v>0.0063</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4292</v>
+        <v>-0.42</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0195</v>
+        <v>0.06</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0195</v>
+        <v>0.06</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0195</v>
+        <v>0.06</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0195</v>
+        <v>0.06</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0195</v>
+        <v>0.06</v>
       </c>
       <c r="N26" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>AZK</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0195</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0021</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.453</v>
+        <v>-0.4517</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0195</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0195</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0195</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0195</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0195</v>
       </c>
       <c r="N27" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1296</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0136</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4737</v>
+        <v>-0.4751</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1296</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1296</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1296</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1296</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1296</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>swag</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1956</v>
+        <v>-0.1296</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0206</v>
+        <v>-0.0136</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5004</v>
+        <v>-0.4955</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1956</v>
+        <v>-0.1296</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1956</v>
+        <v>-0.1296</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1956</v>
+        <v>-0.1296</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1956</v>
+        <v>-0.1296</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1956</v>
+        <v>-0.1296</v>
       </c>
       <c r="N29" t="n">
         <v>92</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pollo</t>
+          <t>swag</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4036</v>
+        <v>-0.1956</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0425</v>
+        <v>-0.0206</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5844</v>
+        <v>-0.5218</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4036</v>
+        <v>-0.1956</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4036</v>
+        <v>-0.1956</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4036</v>
+        <v>-0.1956</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4036</v>
+        <v>-0.1956</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4036</v>
+        <v>-0.1956</v>
       </c>
       <c r="N30" t="n">
         <v>92</v>
@@ -1826,231 +1826,231 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Pollo</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4991</v>
+        <v>-0.4036</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0525</v>
+        <v>-0.0425</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.623</v>
+        <v>-0.6047</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4991</v>
+        <v>-0.4036</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4991</v>
+        <v>-0.4036</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4991</v>
+        <v>-0.4036</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4991</v>
+        <v>-0.4036</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4991</v>
+        <v>-0.4036</v>
       </c>
       <c r="N31" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5115</v>
+        <v>-0.4037</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0538</v>
+        <v>-0.0425</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.628</v>
+        <v>-0.6047</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5115</v>
+        <v>-0.4037</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6609</v>
+        <v>-0.4037</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1494</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6609</v>
+        <v>-0.4037</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5357</v>
+        <v>-0.4037</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1494</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="L32" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3863</v>
+        <v>-0.4037</v>
       </c>
       <c r="N32" t="n">
-        <v>226</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5322</v>
+        <v>-0.4863</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.056</v>
+        <v>-0.0512</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6364</v>
+        <v>-0.6377</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5322</v>
+        <v>-0.4863</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5322</v>
+        <v>-0.0216</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.4647</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5322</v>
+        <v>-0.0216</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5322</v>
+        <v>-0.0175</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.4647</v>
       </c>
       <c r="K33" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5322</v>
+        <v>-0.4822</v>
       </c>
       <c r="N33" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5658</v>
+        <v>-0.5115</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0596</v>
+        <v>-0.0538</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6499</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5658</v>
+        <v>-0.5115</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1011</v>
+        <v>-0.6609</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.4647</v>
+        <v>0.1494</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1011</v>
+        <v>-0.6609</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.082</v>
+        <v>-0.5357</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.4647</v>
+        <v>0.1494</v>
       </c>
       <c r="K34" t="n">
-        <v>51</v>
+        <v>149</v>
       </c>
       <c r="L34" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5467</v>
+        <v>-0.3863</v>
       </c>
       <c r="N34" t="n">
-        <v>95</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6866</v>
+        <v>-0.5322</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0723</v>
+        <v>-0.056</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6987</v>
+        <v>-0.6559</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6866</v>
+        <v>-0.5322</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6866</v>
+        <v>-0.5322</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6866</v>
+        <v>-0.5322</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6866</v>
+        <v>-0.5322</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6866</v>
+        <v>-0.5322</v>
       </c>
       <c r="N35" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36">
@@ -2066,7 +2066,7 @@
         <v>-0.0949</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7856</v>
+        <v>-0.8031</v>
       </c>
       <c r="E36" t="n">
         <v>-0.9016999999999999</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1335</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9338</v>
+        <v>-0.9493</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2686</v>
@@ -2158,7 +2158,7 @@
         <v>-0.1345</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9377</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="E38" t="n">
         <v>-1.2781</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3493</v>
+        <v>-1.3443</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.142</v>
+        <v>-0.1415</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9664</v>
+        <v>-0.9795</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3493</v>
+        <v>-1.3443</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3493</v>
+        <v>-1.3443</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3493</v>
+        <v>-1.3443</v>
       </c>
       <c r="I39" t="n">
         <v>-1.3556</v>
@@ -2250,7 +2250,7 @@
         <v>-0.1512</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0015</v>
+        <v>-1.0161</v>
       </c>
       <c r="E40" t="n">
         <v>-1.4361</v>
@@ -2296,7 +2296,7 @@
         <v>-0.1803</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1131</v>
+        <v>-1.1261</v>
       </c>
       <c r="E41" t="n">
         <v>-1.7124</v>

--- a/database/event/3425/event_3425_evp_summary.xlsx
+++ b/database/event/3425/event_3425_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.2307</v>
+        <v>6.5552</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7612</v>
+        <v>0.6901</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4368</v>
+        <v>2.3213</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2307</v>
+        <v>6.5552</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2771</v>
+        <v>4.0139</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9536</v>
+        <v>2.5413</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6473</v>
+        <v>8.6563</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7668</v>
+        <v>4.5009</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9536</v>
+        <v>2.5413</v>
       </c>
       <c r="K2" t="n">
         <v>99</v>
@@ -529,7 +529,7 @@
         <v>97</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7204</v>
+        <v>7.042199999999999</v>
       </c>
       <c r="N2" t="n">
         <v>196</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7744</v>
+        <v>6.0014</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7131</v>
+        <v>0.6318</v>
       </c>
       <c r="D3" t="n">
-        <v>2.255</v>
+        <v>2.0713</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7744</v>
+        <v>6.0014</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2743</v>
+        <v>3.8964</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5001</v>
+        <v>2.105</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6359</v>
+        <v>8.2423</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7575</v>
+        <v>4.2856</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5001</v>
+        <v>2.105</v>
       </c>
       <c r="K3" t="n">
         <v>99</v>
@@ -575,7 +575,7 @@
         <v>97</v>
       </c>
       <c r="M3" t="n">
-        <v>6.2576</v>
+        <v>6.390599999999999</v>
       </c>
       <c r="N3" t="n">
         <v>196</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2017</v>
+        <v>5.1805</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5476</v>
+        <v>0.5453</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6284</v>
+        <v>1.7007</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2017</v>
+        <v>5.1805</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3394</v>
+        <v>2.497</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8623</v>
+        <v>2.6835</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3394</v>
+        <v>3.3114</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7066</v>
+        <v>1.7218</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8623</v>
+        <v>2.6835</v>
       </c>
       <c r="K4" t="n">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="L4" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5689</v>
+        <v>4.4053</v>
       </c>
       <c r="N4" t="n">
-        <v>196</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.002</v>
+        <v>5.0937</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5266</v>
+        <v>0.5362</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5489</v>
+        <v>1.6615</v>
       </c>
       <c r="E5" t="n">
-        <v>5.002</v>
+        <v>5.0937</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1243</v>
+        <v>3.4476</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8777</v>
+        <v>1.6461</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1243</v>
+        <v>6.6608</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7218</v>
+        <v>3.4633</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8777</v>
+        <v>1.6461</v>
       </c>
       <c r="K5" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="L5" t="n">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5995</v>
+        <v>5.1094</v>
       </c>
       <c r="N5" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9168</v>
+        <v>4.9977</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5261</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5149</v>
+        <v>1.6182</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9168</v>
+        <v>4.9977</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1359</v>
+        <v>2.5258</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7809</v>
+        <v>2.4719</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1359</v>
+        <v>3.4132</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7312</v>
+        <v>1.7747</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7809</v>
+        <v>2.4719</v>
       </c>
       <c r="K6" t="n">
         <v>54</v>
@@ -713,7 +713,7 @@
         <v>130</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5121</v>
+        <v>4.2466</v>
       </c>
       <c r="N6" t="n">
         <v>184</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6091</v>
+        <v>4.6262</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4852</v>
+        <v>0.487</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3924</v>
+        <v>1.4505</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6091</v>
+        <v>4.6262</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5061</v>
+        <v>2.5976</v>
       </c>
       <c r="G7" t="n">
-        <v>2.103</v>
+        <v>2.0286</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5061</v>
+        <v>3.666</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0312</v>
+        <v>1.9061</v>
       </c>
       <c r="J7" t="n">
-        <v>2.103</v>
+        <v>2.0286</v>
       </c>
       <c r="K7" t="n">
         <v>54</v>
@@ -759,7 +759,7 @@
         <v>130</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1342</v>
+        <v>3.9347</v>
       </c>
       <c r="N7" t="n">
         <v>184</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0217</v>
+        <v>4.1466</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4234</v>
+        <v>0.4365</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1583</v>
+        <v>1.234</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0217</v>
+        <v>4.1466</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2554</v>
+        <v>4.0676</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2337</v>
+        <v>0.079</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5601</v>
+        <v>8.8452</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6961</v>
+        <v>4.5991</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2337</v>
+        <v>0.079</v>
       </c>
       <c r="K8" t="n">
         <v>99</v>
@@ -805,7 +805,7 @@
         <v>97</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4624</v>
+        <v>4.6781</v>
       </c>
       <c r="N8" t="n">
         <v>196</v>
@@ -814,231 +814,231 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.638</v>
+        <v>3.0678</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2777</v>
+        <v>0.3229</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6071</v>
+        <v>0.7469</v>
       </c>
       <c r="E9" t="n">
-        <v>2.638</v>
+        <v>3.0678</v>
       </c>
       <c r="F9" t="n">
-        <v>2.638</v>
+        <v>2.1818</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.886</v>
       </c>
       <c r="H9" t="n">
-        <v>2.638</v>
+        <v>2.201</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6602</v>
+        <v>1.1444</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.886</v>
       </c>
       <c r="K9" t="n">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6602</v>
+        <v>2.0304</v>
       </c>
       <c r="N9" t="n">
-        <v>162</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3672</v>
+        <v>2.7246</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2492</v>
+        <v>0.2868</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4992</v>
+        <v>0.592</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3672</v>
+        <v>2.7246</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3672</v>
+        <v>2.7089</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.0157</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3672</v>
+        <v>4.0582</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3672</v>
+        <v>2.1101</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.0157</v>
       </c>
       <c r="K10" t="n">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3672</v>
+        <v>2.1258</v>
       </c>
       <c r="N10" t="n">
-        <v>83</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3561</v>
+        <v>2.6747</v>
       </c>
       <c r="C11" t="n">
-        <v>0.248</v>
+        <v>0.2816</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4948</v>
+        <v>0.5695</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3561</v>
+        <v>2.6747</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5701</v>
+        <v>2.6747</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.214</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5701</v>
+        <v>2.6747</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0831</v>
+        <v>2.7847</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.214</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="L11" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8691</v>
+        <v>2.7847</v>
       </c>
       <c r="N11" t="n">
-        <v>226</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.009</v>
+        <v>2.2718</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2115</v>
+        <v>0.2391</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3565</v>
+        <v>0.3876</v>
       </c>
       <c r="E12" t="n">
-        <v>2.009</v>
+        <v>2.2718</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9964</v>
+        <v>2.2718</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0126</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9964</v>
+        <v>2.2718</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8076</v>
+        <v>2.2718</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0126</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="L12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8202</v>
+        <v>2.2718</v>
       </c>
       <c r="N12" t="n">
-        <v>226</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7584</v>
+        <v>2.2566</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1851</v>
+        <v>0.2375</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2566</v>
+        <v>0.3807</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7584</v>
+        <v>2.2566</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2069</v>
+        <v>2.0579</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5515</v>
+        <v>0.1987</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2069</v>
+        <v>2.0579</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1677</v>
+        <v>1.07</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5515</v>
+        <v>0.1987</v>
       </c>
       <c r="K13" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="L13" t="n">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7192</v>
+        <v>1.2687</v>
       </c>
       <c r="N13" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6948</v>
+        <v>2.235</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1784</v>
+        <v>0.2353</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2313</v>
+        <v>0.371</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6948</v>
+        <v>2.235</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4971</v>
+        <v>2.6903</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8023</v>
+        <v>-0.4553</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4971</v>
+        <v>3.9925</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0239</v>
+        <v>2.0759</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8023</v>
+        <v>-0.4553</v>
       </c>
       <c r="K14" t="n">
         <v>149</v>
@@ -1081,7 +1081,7 @@
         <v>77</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2216</v>
+        <v>1.6206</v>
       </c>
       <c r="N14" t="n">
         <v>226</v>
@@ -1090,216 +1090,216 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4327</v>
+        <v>2.0197</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1508</v>
+        <v>0.2126</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1269</v>
+        <v>0.2738</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4327</v>
+        <v>2.0197</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3096</v>
+        <v>0.9155</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8769</v>
+        <v>1.1042</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3096</v>
+        <v>0.9155</v>
       </c>
       <c r="I15" t="n">
-        <v>1.872</v>
+        <v>0.476</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8769</v>
+        <v>1.1042</v>
       </c>
       <c r="K15" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L15" t="n">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9951000000000001</v>
+        <v>1.5802</v>
       </c>
       <c r="N15" t="n">
-        <v>95</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GruBy</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3847</v>
+        <v>1.9372</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1458</v>
+        <v>0.2039</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1078</v>
+        <v>0.2365</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3847</v>
+        <v>1.9372</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3847</v>
+        <v>2.5443</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.6071</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3847</v>
+        <v>3.4784</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3964</v>
+        <v>1.8086</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.6071</v>
       </c>
       <c r="K16" t="n">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3964</v>
+        <v>1.2015</v>
       </c>
       <c r="N16" t="n">
-        <v>162</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3451</v>
+        <v>1.8731</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1416</v>
+        <v>0.1972</v>
       </c>
       <c r="D17" t="n">
-        <v>0.092</v>
+        <v>0.2076</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3451</v>
+        <v>1.8731</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4157</v>
+        <v>2.4703</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9294</v>
+        <v>-0.5972</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4157</v>
+        <v>3.2176</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3369</v>
+        <v>1.673</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9294</v>
+        <v>-0.5972</v>
       </c>
       <c r="K17" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L17" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2663</v>
+        <v>1.0758</v>
       </c>
       <c r="N17" t="n">
-        <v>184</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2876</v>
+        <v>1.7401</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1355</v>
+        <v>0.1832</v>
       </c>
       <c r="D18" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.1476</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2876</v>
+        <v>1.7401</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1059</v>
+        <v>0.4843</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8183</v>
+        <v>1.2558</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1059</v>
+        <v>0.4843</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7069</v>
+        <v>0.2518</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8183</v>
+        <v>1.2558</v>
       </c>
       <c r="K18" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L18" t="n">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8886000000000001</v>
+        <v>1.5076</v>
       </c>
       <c r="N18" t="n">
-        <v>95</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>phr</t>
+          <t>GruBy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2848</v>
+        <v>1.7093</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1352</v>
+        <v>0.1799</v>
       </c>
       <c r="D19" t="n">
-        <v>0.068</v>
+        <v>0.1336</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2848</v>
+        <v>1.7093</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2848</v>
+        <v>1.7093</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2848</v>
+        <v>1.7093</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2956</v>
+        <v>1.7796</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2956</v>
+        <v>1.7796</v>
       </c>
       <c r="N19" t="n">
         <v>162</v>
@@ -1320,262 +1320,262 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>freddieb</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1554</v>
+        <v>1.5099</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1216</v>
+        <v>0.1589</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0164</v>
+        <v>0.0436</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1554</v>
+        <v>1.5099</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1554</v>
+        <v>1.8238</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.3139</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1554</v>
+        <v>1.8238</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1652</v>
+        <v>0.9483</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.3139</v>
       </c>
       <c r="K20" t="n">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1652</v>
+        <v>0.6344000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>162</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>freddieb</t>
+          <t>phr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6002999999999999</v>
+        <v>1.5082</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.1588</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2048</v>
+        <v>0.0429</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6002999999999999</v>
+        <v>1.5082</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0042</v>
+        <v>1.5082</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4039</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0042</v>
+        <v>1.5082</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8139</v>
+        <v>1.5702</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4039</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="L21" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.41</v>
+        <v>1.5702</v>
       </c>
       <c r="N21" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>disco doplan</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5828</v>
+        <v>1.5063</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0614</v>
+        <v>0.1586</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2117</v>
+        <v>0.042</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5828</v>
+        <v>1.5063</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5828</v>
+        <v>1.5063</v>
       </c>
       <c r="G22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5828</v>
+        <v>1.5063</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2829</v>
+        <v>1.5682</v>
       </c>
       <c r="J22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="L22" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2828999999999999</v>
+        <v>1.5682</v>
       </c>
       <c r="N22" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>disco doplan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5601</v>
+        <v>1.488</v>
       </c>
       <c r="C23" t="n">
-        <v>0.059</v>
+        <v>0.1566</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2208</v>
+        <v>0.0337</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5601</v>
+        <v>1.488</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5601</v>
+        <v>2.3004</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.8124</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5601</v>
+        <v>2.6189</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5601</v>
+        <v>1.3617</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.8124</v>
       </c>
       <c r="K23" t="n">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5601</v>
+        <v>0.5492999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5454</v>
+        <v>0.6035</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0574</v>
+        <v>0.0635</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2266</v>
+        <v>-0.3656</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5454</v>
+        <v>0.6035</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6593</v>
+        <v>0.6035</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1139</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6593</v>
+        <v>0.6035</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5344</v>
+        <v>0.6035</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1139</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="L24" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4205</v>
+        <v>0.6035</v>
       </c>
       <c r="N24" t="n">
-        <v>196</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2062</v>
+        <v>0.2844</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0217</v>
+        <v>0.0299</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3618</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2062</v>
+        <v>0.2844</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2062</v>
+        <v>0.2844</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2062</v>
+        <v>0.2844</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2062</v>
+        <v>0.2844</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2062</v>
+        <v>0.2844</v>
       </c>
       <c r="N25" t="n">
         <v>83</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nukkye</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.06</v>
+        <v>0.2159</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0063</v>
+        <v>0.0227</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.42</v>
+        <v>-0.5405</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06</v>
+        <v>0.2159</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06</v>
+        <v>0.2159</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.06</v>
+        <v>0.2159</v>
       </c>
       <c r="I26" t="n">
-        <v>0.06</v>
+        <v>0.2159</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.06</v>
+        <v>0.2159</v>
       </c>
       <c r="N26" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0195</v>
+        <v>0.1605</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0021</v>
+        <v>0.0169</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4517</v>
+        <v>-0.5656</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0195</v>
+        <v>0.1605</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0195</v>
+        <v>0.1605</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0195</v>
+        <v>0.1605</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0195</v>
+        <v>0.1605</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0195</v>
+        <v>0.1605</v>
       </c>
       <c r="N27" t="n">
         <v>92</v>
@@ -1688,78 +1688,78 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.1578</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0166</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4751</v>
+        <v>-0.5668</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.1578</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.1578</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.1578</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.1578</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.1578</v>
       </c>
       <c r="N28" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>swag</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1296</v>
+        <v>0.1332</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0136</v>
+        <v>0.014</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4955</v>
+        <v>-0.5779</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1296</v>
+        <v>0.1332</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1296</v>
+        <v>0.1332</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1296</v>
+        <v>0.1332</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1296</v>
+        <v>0.1332</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1296</v>
+        <v>0.1332</v>
       </c>
       <c r="N29" t="n">
         <v>92</v>
@@ -1780,139 +1780,139 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>swag</t>
+          <t>nukkye</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1956</v>
+        <v>0.0948</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0206</v>
+        <v>0.01</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5218</v>
+        <v>-0.5952</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1956</v>
+        <v>0.0948</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1956</v>
+        <v>0.0948</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1956</v>
+        <v>0.0948</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1956</v>
+        <v>0.0948</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1956</v>
+        <v>0.0948</v>
       </c>
       <c r="N30" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pollo</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4036</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0425</v>
+        <v>-0.0009</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6047</v>
+        <v>-0.642</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4036</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4036</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4036</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4036</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4036</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Pollo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4037</v>
+        <v>-0.0762</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0425</v>
+        <v>-0.008</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6047</v>
+        <v>-0.6724</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4037</v>
+        <v>-0.0762</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4037</v>
+        <v>-0.0762</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4037</v>
+        <v>-0.0762</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4037</v>
+        <v>-0.0762</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4037</v>
+        <v>-0.0762</v>
       </c>
       <c r="N32" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4863</v>
+        <v>-0.2776</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0512</v>
+        <v>-0.0292</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6377</v>
+        <v>-0.7633</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4863</v>
+        <v>-0.2776</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0216</v>
+        <v>0.0789</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4647</v>
+        <v>-0.3565</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.0216</v>
+        <v>0.0789</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0175</v>
+        <v>0.041</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4647</v>
+        <v>-0.3565</v>
       </c>
       <c r="K33" t="n">
         <v>51</v>
@@ -1955,7 +1955,7 @@
         <v>44</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4822</v>
+        <v>-0.3155</v>
       </c>
       <c r="N33" t="n">
         <v>95</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5115</v>
+        <v>-0.3675</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0538</v>
+        <v>-0.0387</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5115</v>
+        <v>-0.3675</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6609</v>
+        <v>-0.5085</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1494</v>
+        <v>0.141</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6609</v>
+        <v>-0.5085</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5357</v>
+        <v>-0.2644</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1494</v>
+        <v>0.141</v>
       </c>
       <c r="K34" t="n">
         <v>149</v>
@@ -2001,7 +2001,7 @@
         <v>77</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3863</v>
+        <v>-0.1234</v>
       </c>
       <c r="N34" t="n">
         <v>226</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5322</v>
+        <v>-0.3683</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.056</v>
+        <v>-0.0388</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6559</v>
+        <v>-0.8043</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5322</v>
+        <v>-0.3683</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5322</v>
+        <v>-0.3683</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5322</v>
+        <v>-0.3683</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5322</v>
+        <v>-0.3683</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5322</v>
+        <v>-0.3683</v>
       </c>
       <c r="N35" t="n">
         <v>70</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.5607</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0949</v>
+        <v>-0.059</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8031</v>
+        <v>-0.8911</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.5607</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.5607</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.5607</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.5607</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.5607</v>
       </c>
       <c r="N36" t="n">
         <v>70</v>
@@ -2102,139 +2102,139 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EspiranTo</t>
+          <t>hAdji</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2686</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1335</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9493</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2686</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2686</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2686</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2686</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2686</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hAdji</t>
+          <t>TOAO</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2781</v>
+        <v>-1.0607</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1345</v>
+        <v>-0.1117</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-1.1169</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2781</v>
+        <v>-1.0607</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2781</v>
+        <v>-1.0607</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2781</v>
+        <v>-1.0607</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2781</v>
+        <v>-1.1043</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2781</v>
+        <v>-1.1043</v>
       </c>
       <c r="N38" t="n">
-        <v>83</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TOAO</t>
+          <t>EspiranTo</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3443</v>
+        <v>-1.1687</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1415</v>
+        <v>-0.123</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9795</v>
+        <v>-1.1656</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3443</v>
+        <v>-1.1687</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3443</v>
+        <v>-1.1687</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3443</v>
+        <v>-1.1687</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3556</v>
+        <v>-1.1687</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3556</v>
+        <v>-1.1687</v>
       </c>
       <c r="N39" t="n">
-        <v>162</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4361</v>
+        <v>-1.2408</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1512</v>
+        <v>-0.1306</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0161</v>
+        <v>-1.1982</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4361</v>
+        <v>-1.2408</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4361</v>
+        <v>-1.2408</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4361</v>
+        <v>-1.2408</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4361</v>
+        <v>-1.2408</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4361</v>
+        <v>-1.2408</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.7124</v>
+        <v>-1.5459</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1803</v>
+        <v>-0.1627</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1261</v>
+        <v>-1.3359</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.7124</v>
+        <v>-1.5459</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.8987000000000001</v>
+        <v>-1.0445</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8137</v>
+        <v>-0.5014</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.8987000000000001</v>
+        <v>-1.0445</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7284</v>
+        <v>-0.5431</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8137</v>
+        <v>-0.5014</v>
       </c>
       <c r="K41" t="n">
         <v>149</v>
@@ -2323,7 +2323,7 @@
         <v>77</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5421</v>
+        <v>-1.0445</v>
       </c>
       <c r="N41" t="n">
         <v>226</v>
@@ -2429,10 +2429,10 @@
         <v>1.36</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9265</v>
+        <v>0.9277</v>
       </c>
       <c r="J2" t="n">
-        <v>25.942</v>
+        <v>25.9756</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.28</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7417</v>
+        <v>0.7463</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7676</v>
+        <v>20.8964</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6143</v>
+        <v>0.6298</v>
       </c>
       <c r="J4" t="n">
-        <v>17.2004</v>
+        <v>17.6344</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.08</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1754</v>
+        <v>0.2439</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9112</v>
+        <v>6.8292</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.07</v>
       </c>
       <c r="I6" t="n">
-        <v>0.145</v>
+        <v>0.2139</v>
       </c>
       <c r="J6" t="n">
-        <v>4.06</v>
+        <v>5.9892</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4584</v>
+        <v>0.5282</v>
       </c>
       <c r="J7" t="n">
-        <v>12.8352</v>
+        <v>14.7896</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1966</v>
+        <v>-0.1432</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.5048</v>
+        <v>-4.0096</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.84</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2794</v>
+        <v>-0.1834</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.8232</v>
+        <v>-5.1352</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4642</v>
+        <v>-0.3014</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.9976</v>
+        <v>-8.4392</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4921</v>
+        <v>-0.3205</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.7788</v>
+        <v>-8.974</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.41</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0616</v>
+        <v>1.0339</v>
       </c>
       <c r="J12" t="n">
-        <v>26.54</v>
+        <v>25.8475</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7246</v>
+        <v>0.7137</v>
       </c>
       <c r="J13" t="n">
-        <v>18.115</v>
+        <v>17.8425</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.23</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6504</v>
+        <v>0.6418</v>
       </c>
       <c r="J14" t="n">
-        <v>16.26</v>
+        <v>16.045</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.07</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1704</v>
+        <v>0.2265</v>
       </c>
       <c r="J15" t="n">
-        <v>4.26</v>
+        <v>5.6625</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.79</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.6891</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.535</v>
+        <v>-17.2275</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.26</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4693</v>
+        <v>0.5491</v>
       </c>
       <c r="J17" t="n">
-        <v>11.7325</v>
+        <v>13.7275</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3857</v>
+        <v>0.4406</v>
       </c>
       <c r="J18" t="n">
-        <v>9.6425</v>
+        <v>11.015</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2636</v>
+        <v>0.2882</v>
       </c>
       <c r="J19" t="n">
-        <v>6.59</v>
+        <v>7.205</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.72</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4928</v>
+        <v>-0.3165</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.32</v>
+        <v>-7.9125</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.67</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5579</v>
+        <v>-0.3638</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.9475</v>
+        <v>-9.095000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0046</v>
+        <v>-0.0325</v>
       </c>
       <c r="J22" t="n">
-        <v>0.092</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.67</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4603</v>
+        <v>-0.3225</v>
       </c>
       <c r="J23" t="n">
-        <v>-9.206</v>
+        <v>-6.45</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.66</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4776</v>
+        <v>-0.3315</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.552</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4942</v>
+        <v>-0.3406</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.884</v>
+        <v>-6.812</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.51</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.695</v>
+        <v>-0.4711</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.9</v>
+        <v>-9.422000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.76</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6098</v>
+        <v>1.133</v>
       </c>
       <c r="J27" t="n">
-        <v>32.196</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.39</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8423</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>16.846</v>
+        <v>13.902</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.36</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7735</v>
+        <v>0.6575</v>
       </c>
       <c r="J29" t="n">
-        <v>15.47</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.35</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7509</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>15.018</v>
+        <v>12.894</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.28</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5928</v>
+        <v>0.5525</v>
       </c>
       <c r="J31" t="n">
-        <v>11.856</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>0.98</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0564</v>
+        <v>0.0086</v>
       </c>
       <c r="J32" t="n">
-        <v>1.3536</v>
+        <v>0.2064</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.96</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0129</v>
+        <v>-0.025</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3096</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.74</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3827</v>
+        <v>-0.2665</v>
       </c>
       <c r="J34" t="n">
-        <v>-9.184799999999999</v>
+        <v>-6.396</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.66</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5099</v>
+        <v>-0.3413</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.2376</v>
+        <v>-8.1912</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.42</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8229</v>
+        <v>-0.5647</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.7496</v>
+        <v>-13.5528</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.77</v>
       </c>
       <c r="I37" t="n">
-        <v>1.6758</v>
+        <v>1.1724</v>
       </c>
       <c r="J37" t="n">
-        <v>40.2192</v>
+        <v>28.1376</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.38</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9137</v>
+        <v>0.6938</v>
       </c>
       <c r="J38" t="n">
-        <v>21.9288</v>
+        <v>16.6512</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.28</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6522</v>
+        <v>0.5661</v>
       </c>
       <c r="J39" t="n">
-        <v>15.6528</v>
+        <v>13.5864</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.08</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1352</v>
+        <v>0.2192</v>
       </c>
       <c r="J40" t="n">
-        <v>3.2448</v>
+        <v>5.2608</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.03</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0223</v>
+        <v>0.0585</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5352</v>
+        <v>1.404</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.11</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2887</v>
+        <v>0.233</v>
       </c>
       <c r="J42" t="n">
-        <v>8.372299999999999</v>
+        <v>6.757</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0859</v>
+        <v>-0.0772</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.4911</v>
+        <v>-2.2388</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.9</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1645</v>
+        <v>-0.1231</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.7705</v>
+        <v>-3.5699</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.82</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3184</v>
+        <v>-0.2049</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.233599999999999</v>
+        <v>-5.9421</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.65</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5622</v>
+        <v>-0.3694</v>
       </c>
       <c r="J46" t="n">
-        <v>-16.3038</v>
+        <v>-10.7126</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.37</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5536</v>
+        <v>0.422</v>
       </c>
       <c r="J47" t="n">
-        <v>16.0544</v>
+        <v>12.238</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.3</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4631</v>
+        <v>0.3744</v>
       </c>
       <c r="J48" t="n">
-        <v>13.4299</v>
+        <v>10.8576</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.24</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3795</v>
+        <v>0.3288</v>
       </c>
       <c r="J49" t="n">
-        <v>11.0055</v>
+        <v>9.5352</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0164</v>
       </c>
       <c r="J50" t="n">
-        <v>-1.9024</v>
+        <v>-0.4756</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.97</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1451</v>
+        <v>-0.0677</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.2079</v>
+        <v>-1.9633</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.6496</v>
       </c>
       <c r="J52" t="n">
-        <v>23.6115</v>
+        <v>17.5392</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6854</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>18.5058</v>
+        <v>14.5746</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.2</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5541</v>
+        <v>0.4694</v>
       </c>
       <c r="J54" t="n">
-        <v>14.9607</v>
+        <v>12.6738</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.11</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2781</v>
+        <v>0.3321</v>
       </c>
       <c r="J55" t="n">
-        <v>7.5087</v>
+        <v>8.966699999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.99</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1728</v>
+        <v>-0.0975</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.6656</v>
+        <v>-2.6325</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.17</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3509</v>
+        <v>0.3689</v>
       </c>
       <c r="J57" t="n">
-        <v>9.474299999999999</v>
+        <v>9.9603</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.09</v>
       </c>
       <c r="I58" t="n">
-        <v>0.223</v>
+        <v>0.2341</v>
       </c>
       <c r="J58" t="n">
-        <v>6.021</v>
+        <v>6.3207</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.93</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1614</v>
+        <v>-0.0968</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.3578</v>
+        <v>-2.6136</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.88</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2512</v>
+        <v>-0.1525</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.7824</v>
+        <v>-4.1175</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.77</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4189</v>
+        <v>-0.265</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.3103</v>
+        <v>-7.155</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.57</v>
       </c>
       <c r="I62" t="n">
-        <v>1.2669</v>
+        <v>0.9149</v>
       </c>
       <c r="J62" t="n">
-        <v>26.6049</v>
+        <v>19.2129</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.48</v>
       </c>
       <c r="I63" t="n">
-        <v>1.083</v>
+        <v>0.8064</v>
       </c>
       <c r="J63" t="n">
-        <v>22.743</v>
+        <v>16.9344</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.39</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8643</v>
+        <v>0.6976</v>
       </c>
       <c r="J64" t="n">
-        <v>18.1503</v>
+        <v>14.6496</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.38</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8386</v>
+        <v>0.6854</v>
       </c>
       <c r="J65" t="n">
-        <v>17.6106</v>
+        <v>14.3934</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.17</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3442</v>
+        <v>0.3995</v>
       </c>
       <c r="J66" t="n">
-        <v>7.2282</v>
+        <v>8.3895</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.05</v>
       </c>
       <c r="I67" t="n">
-        <v>0.236</v>
+        <v>0.2299</v>
       </c>
       <c r="J67" t="n">
-        <v>4.956</v>
+        <v>4.8279</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.87</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1523</v>
+        <v>-0.1366</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.1983</v>
+        <v>-2.8686</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.72</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4198</v>
+        <v>-0.2855</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.815799999999999</v>
+        <v>-5.9955</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.67</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4969</v>
+        <v>-0.3325</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.4349</v>
+        <v>-6.9825</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.47</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7629</v>
+        <v>-0.5191</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.0209</v>
+        <v>-10.9011</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.08</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3043</v>
+        <v>0.3213</v>
       </c>
       <c r="J72" t="n">
-        <v>6.6946</v>
+        <v>7.0686</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.91</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0692</v>
+        <v>-0.0829</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.5224</v>
+        <v>-1.8238</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.71</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.4181</v>
+        <v>-0.2911</v>
       </c>
       <c r="J74" t="n">
-        <v>-9.1982</v>
+        <v>-6.4042</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.57</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6268</v>
+        <v>-0.4215</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.7896</v>
+        <v>-9.273</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.36</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8901</v>
+        <v>-0.6168</v>
       </c>
       <c r="J76" t="n">
-        <v>-19.5822</v>
+        <v>-13.5696</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.86</v>
       </c>
       <c r="I77" t="n">
-        <v>1.7775</v>
+        <v>1.5173</v>
       </c>
       <c r="J77" t="n">
-        <v>39.105</v>
+        <v>33.3806</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.83</v>
       </c>
       <c r="I78" t="n">
-        <v>1.7254</v>
+        <v>1.4831</v>
       </c>
       <c r="J78" t="n">
-        <v>37.9588</v>
+        <v>32.6282</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4481</v>
+        <v>0.5589</v>
       </c>
       <c r="J79" t="n">
-        <v>9.8582</v>
+        <v>12.2958</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.19</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3773</v>
+        <v>0.485</v>
       </c>
       <c r="J80" t="n">
-        <v>8.300599999999999</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.14</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2548</v>
+        <v>0.3562</v>
       </c>
       <c r="J81" t="n">
-        <v>5.6056</v>
+        <v>7.8364</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.92</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0105</v>
+        <v>-0.0267</v>
       </c>
       <c r="J82" t="n">
-        <v>0.189</v>
+        <v>-0.4806</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.58</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.5574</v>
+        <v>-0.3917</v>
       </c>
       <c r="J83" t="n">
-        <v>-10.0332</v>
+        <v>-7.0506</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.5904</v>
+        <v>-0.4099</v>
       </c>
       <c r="J84" t="n">
-        <v>-10.6272</v>
+        <v>-7.3782</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.51</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.4563</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.9844</v>
+        <v>-8.2134</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.45</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7494</v>
+        <v>-0.513</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.4892</v>
+        <v>-9.234</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>2.27</v>
       </c>
       <c r="I87" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J87" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.6</v>
       </c>
       <c r="I88" t="n">
-        <v>1.2554</v>
+        <v>1.2048</v>
       </c>
       <c r="J88" t="n">
-        <v>22.5972</v>
+        <v>21.6864</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.43</v>
       </c>
       <c r="I89" t="n">
-        <v>0.874</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>15.732</v>
+        <v>17.973</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.29</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5766</v>
+        <v>0.7046</v>
       </c>
       <c r="J90" t="n">
-        <v>10.3788</v>
+        <v>12.6828</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.13</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2062</v>
+        <v>0.3102</v>
       </c>
       <c r="J91" t="n">
-        <v>3.7116</v>
+        <v>5.5836</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3288</v>
+        <v>0.2865</v>
       </c>
       <c r="J92" t="n">
-        <v>8.220000000000001</v>
+        <v>7.1625</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.13</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2663</v>
+        <v>0.2285</v>
       </c>
       <c r="J93" t="n">
-        <v>6.6575</v>
+        <v>5.7125</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.07</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1612</v>
+        <v>0.1358</v>
       </c>
       <c r="J94" t="n">
-        <v>4.03</v>
+        <v>3.395</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.91</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2198</v>
+        <v>-0.1263</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.495</v>
+        <v>-3.1575</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.87</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2856</v>
+        <v>-0.1703</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.14</v>
+        <v>-4.2575</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7099</v>
+        <v>0.6292</v>
       </c>
       <c r="J97" t="n">
-        <v>17.7475</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.41</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6036</v>
+        <v>0.529</v>
       </c>
       <c r="J98" t="n">
-        <v>15.09</v>
+        <v>13.225</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.14</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2108</v>
+        <v>0.2094</v>
       </c>
       <c r="J99" t="n">
-        <v>5.27</v>
+        <v>5.235</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.93</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2194</v>
+        <v>-0.1183</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.485</v>
+        <v>-2.9575</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.89</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2849</v>
+        <v>-0.1638</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.1225</v>
+        <v>-4.095</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.35</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9343</v>
+        <v>0.9246</v>
       </c>
       <c r="J102" t="n">
-        <v>27.0947</v>
+        <v>26.8134</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.25</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7027</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>20.3783</v>
+        <v>20.039</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.15</v>
       </c>
       <c r="I104" t="n">
-        <v>0.428</v>
+        <v>0.446</v>
       </c>
       <c r="J104" t="n">
-        <v>12.412</v>
+        <v>12.934</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1075</v>
+        <v>0.1651</v>
       </c>
       <c r="J105" t="n">
-        <v>3.1175</v>
+        <v>4.7879</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.342</v>
+        <v>-0.2693</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.917999999999999</v>
+        <v>-7.8097</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.01</v>
       </c>
       <c r="I107" t="n">
-        <v>0.0794</v>
+        <v>0.0544</v>
       </c>
       <c r="J107" t="n">
-        <v>2.3026</v>
+        <v>1.5776</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0794</v>
+        <v>0.0544</v>
       </c>
       <c r="J108" t="n">
-        <v>2.3026</v>
+        <v>1.5776</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.95</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0837</v>
+        <v>-0.0692</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.4273</v>
+        <v>-2.0068</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.91</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.175</v>
+        <v>-0.115</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.075</v>
+        <v>-3.335</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.72</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4768</v>
+        <v>-0.3076</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.8272</v>
+        <v>-8.920400000000001</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.58</v>
       </c>
       <c r="I112" t="n">
-        <v>1.4182</v>
+        <v>1.2666</v>
       </c>
       <c r="J112" t="n">
-        <v>42.546</v>
+        <v>37.998</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.19</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5663</v>
+        <v>0.5517</v>
       </c>
       <c r="J113" t="n">
-        <v>16.989</v>
+        <v>16.551</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.09</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2525</v>
+        <v>0.2917</v>
       </c>
       <c r="J114" t="n">
-        <v>7.575</v>
+        <v>8.750999999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.91</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4221</v>
+        <v>-0.3539</v>
       </c>
       <c r="J115" t="n">
-        <v>-12.663</v>
+        <v>-10.617</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.5502</v>
       </c>
       <c r="J116" t="n">
-        <v>-18.312</v>
+        <v>-16.506</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.422</v>
+        <v>0.4893</v>
       </c>
       <c r="J117" t="n">
-        <v>12.66</v>
+        <v>14.679</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.03</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0858</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>2.574</v>
+        <v>2.697</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.03</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0858</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>2.574</v>
+        <v>2.697</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.93</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1785</v>
+        <v>-0.1013</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.355</v>
+        <v>-3.039</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3274</v>
+        <v>-0.1997</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.821999999999999</v>
+        <v>-5.991</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.02</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2179</v>
+        <v>0.2116</v>
       </c>
       <c r="J122" t="n">
-        <v>4.5759</v>
+        <v>4.4436</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.79</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2354</v>
+        <v>-0.2016</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.9434</v>
+        <v>-4.2336</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.59</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.5746</v>
+        <v>-0.3922</v>
       </c>
       <c r="J124" t="n">
-        <v>-12.0666</v>
+        <v>-8.2362</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.54</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6464</v>
+        <v>-0.4388</v>
       </c>
       <c r="J125" t="n">
-        <v>-13.5744</v>
+        <v>-9.2148</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.37</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.867</v>
+        <v>-0.5987</v>
       </c>
       <c r="J126" t="n">
-        <v>-18.207</v>
+        <v>-12.5727</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.8</v>
       </c>
       <c r="I127" t="n">
-        <v>1.6346</v>
+        <v>1.4319</v>
       </c>
       <c r="J127" t="n">
-        <v>34.3266</v>
+        <v>30.0699</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.73</v>
       </c>
       <c r="I128" t="n">
-        <v>1.5079</v>
+        <v>1.3529</v>
       </c>
       <c r="J128" t="n">
-        <v>31.6659</v>
+        <v>28.4109</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.71</v>
       </c>
       <c r="I129" t="n">
-        <v>1.4708</v>
+        <v>1.3303</v>
       </c>
       <c r="J129" t="n">
-        <v>30.8868</v>
+        <v>27.9363</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.47</v>
       </c>
       <c r="I130" t="n">
-        <v>0.9592000000000001</v>
+        <v>1.0551</v>
       </c>
       <c r="J130" t="n">
-        <v>20.1432</v>
+        <v>22.1571</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2109</v>
+        <v>-0.1227</v>
       </c>
       <c r="J131" t="n">
-        <v>-4.4289</v>
+        <v>-2.5767</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1066</v>
+        <v>0.0809</v>
       </c>
       <c r="J132" t="n">
-        <v>2.0254</v>
+        <v>1.5371</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.9</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0259</v>
+        <v>-0.0539</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.4921</v>
+        <v>-1.0241</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.44</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.7635</v>
+        <v>-0.5229</v>
       </c>
       <c r="J134" t="n">
-        <v>-14.5065</v>
+        <v>-9.9351</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.42</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.7901</v>
+        <v>-0.542</v>
       </c>
       <c r="J135" t="n">
-        <v>-15.0119</v>
+        <v>-10.298</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.3</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.9419</v>
+        <v>-0.657</v>
       </c>
       <c r="J136" t="n">
-        <v>-17.8961</v>
+        <v>-12.483</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.44</v>
       </c>
       <c r="I137" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J137" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.67</v>
       </c>
       <c r="I138" t="n">
-        <v>1.3444</v>
+        <v>1.2745</v>
       </c>
       <c r="J138" t="n">
-        <v>25.5436</v>
+        <v>24.2155</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.63</v>
       </c>
       <c r="I139" t="n">
-        <v>1.2471</v>
+        <v>1.2311</v>
       </c>
       <c r="J139" t="n">
-        <v>23.6949</v>
+        <v>23.3909</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.32</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.7541</v>
       </c>
       <c r="J140" t="n">
-        <v>11.6736</v>
+        <v>14.3279</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.15</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2353</v>
+        <v>0.3451</v>
       </c>
       <c r="J141" t="n">
-        <v>4.4707</v>
+        <v>6.5569</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.07</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2417</v>
+        <v>0.2399</v>
       </c>
       <c r="J142" t="n">
-        <v>5.8008</v>
+        <v>5.7576</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.01</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1167</v>
+        <v>0.0843</v>
       </c>
       <c r="J143" t="n">
-        <v>2.8008</v>
+        <v>2.0232</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.79</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3433</v>
+        <v>-0.2281</v>
       </c>
       <c r="J144" t="n">
-        <v>-8.2392</v>
+        <v>-5.4744</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.549</v>
+        <v>-0.3621</v>
       </c>
       <c r="J145" t="n">
-        <v>-13.176</v>
+        <v>-8.6904</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.63</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5757</v>
+        <v>-0.3809</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.8168</v>
+        <v>-9.1416</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.83</v>
       </c>
       <c r="I147" t="n">
-        <v>1.7554</v>
+        <v>1.4993</v>
       </c>
       <c r="J147" t="n">
-        <v>42.1296</v>
+        <v>35.9832</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.4</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9165</v>
+        <v>0.9686</v>
       </c>
       <c r="J148" t="n">
-        <v>21.996</v>
+        <v>23.2464</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.39</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8917</v>
+        <v>0.9504</v>
       </c>
       <c r="J149" t="n">
-        <v>21.4008</v>
+        <v>22.8096</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.39</v>
       </c>
       <c r="I150" t="n">
-        <v>0.8917</v>
+        <v>0.9504</v>
       </c>
       <c r="J150" t="n">
-        <v>21.4008</v>
+        <v>22.8096</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.87</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5977</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.3448</v>
+        <v>-12.6648</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.22</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4038</v>
+        <v>0.4675</v>
       </c>
       <c r="J152" t="n">
-        <v>10.9026</v>
+        <v>12.6225</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1827</v>
+        <v>0.1997</v>
       </c>
       <c r="J153" t="n">
-        <v>4.9329</v>
+        <v>5.3919</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.03</v>
       </c>
       <c r="I154" t="n">
-        <v>0.078</v>
+        <v>0.0883</v>
       </c>
       <c r="J154" t="n">
-        <v>2.106</v>
+        <v>2.3841</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1638</v>
+        <v>-0.0906</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.4226</v>
+        <v>-2.4462</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3152</v>
+        <v>-0.1907</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.510400000000001</v>
+        <v>-5.1489</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.29</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8062</v>
+        <v>0.7907</v>
       </c>
       <c r="J157" t="n">
-        <v>21.7674</v>
+        <v>21.3489</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.28</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.767</v>
       </c>
       <c r="J158" t="n">
-        <v>21.1356</v>
+        <v>20.709</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3384</v>
+        <v>0.3715</v>
       </c>
       <c r="J159" t="n">
-        <v>9.136799999999999</v>
+        <v>10.0305</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.12</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3384</v>
+        <v>0.3715</v>
       </c>
       <c r="J160" t="n">
-        <v>9.136799999999999</v>
+        <v>10.0305</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5628</v>
+        <v>-0.4991</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.1956</v>
+        <v>-13.4757</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.52</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2271</v>
+        <v>1.1505</v>
       </c>
       <c r="J162" t="n">
-        <v>29.4504</v>
+        <v>27.612</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.35</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8662</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="J163" t="n">
-        <v>20.7888</v>
+        <v>21.3024</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.34</v>
       </c>
       <c r="I164" t="n">
-        <v>0.843</v>
+        <v>0.8656</v>
       </c>
       <c r="J164" t="n">
-        <v>20.232</v>
+        <v>20.7744</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.19</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4445</v>
+        <v>0.5229</v>
       </c>
       <c r="J165" t="n">
-        <v>10.668</v>
+        <v>12.5496</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.96</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3179</v>
+        <v>-0.2346</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.6296</v>
+        <v>-5.6304</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.15</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3563</v>
+        <v>0.3916</v>
       </c>
       <c r="J167" t="n">
-        <v>8.5512</v>
+        <v>9.398400000000001</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2599</v>
+        <v>0.2667</v>
       </c>
       <c r="J168" t="n">
-        <v>6.2376</v>
+        <v>6.4008</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2215</v>
+        <v>-0.1532</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.316</v>
+        <v>-3.6768</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.66</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5462</v>
+        <v>-0.3584</v>
       </c>
       <c r="J170" t="n">
-        <v>-13.1088</v>
+        <v>-8.601599999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.59</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6367</v>
+        <v>-0.4238</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.2808</v>
+        <v>-10.1712</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.19</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4021</v>
+        <v>0.4542</v>
       </c>
       <c r="J172" t="n">
-        <v>9.650399999999999</v>
+        <v>10.9008</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.15</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3427</v>
+        <v>0.3763</v>
       </c>
       <c r="J173" t="n">
-        <v>8.2248</v>
+        <v>9.0312</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.93</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1187</v>
+        <v>-0.0919</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.8488</v>
+        <v>-2.2056</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.64</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5802</v>
+        <v>-0.3818</v>
       </c>
       <c r="J175" t="n">
-        <v>-13.9248</v>
+        <v>-9.1632</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5931</v>
+        <v>-0.3911</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.2344</v>
+        <v>-9.3864</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>1.356</v>
+        <v>1.2307</v>
       </c>
       <c r="J177" t="n">
-        <v>32.544</v>
+        <v>29.5368</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.55</v>
       </c>
       <c r="I178" t="n">
-        <v>1.2978</v>
+        <v>1.1933</v>
       </c>
       <c r="J178" t="n">
-        <v>31.1472</v>
+        <v>28.6392</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.23</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5647</v>
+        <v>0.6236</v>
       </c>
       <c r="J179" t="n">
-        <v>13.5528</v>
+        <v>14.9664</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.12</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2704</v>
+        <v>0.3468</v>
       </c>
       <c r="J180" t="n">
-        <v>6.4896</v>
+        <v>8.3232</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.76</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8329</v>
+        <v>-0.7876</v>
       </c>
       <c r="J181" t="n">
-        <v>-19.9896</v>
+        <v>-18.9024</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I182" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0837</v>
       </c>
       <c r="J182" t="n">
-        <v>1.8088</v>
+        <v>1.5903</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.52</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.4327</v>
       </c>
       <c r="J183" t="n">
-        <v>-11.3867</v>
+        <v>-8.221299999999999</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.47</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.6864</v>
+        <v>-0.4781</v>
       </c>
       <c r="J184" t="n">
-        <v>-13.0416</v>
+        <v>-9.0839</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.47</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.6864</v>
+        <v>-0.4781</v>
       </c>
       <c r="J185" t="n">
-        <v>-13.0416</v>
+        <v>-9.0839</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.23</v>
       </c>
       <c r="I186" t="n">
-        <v>-1.0136</v>
+        <v>-0.7134</v>
       </c>
       <c r="J186" t="n">
-        <v>-19.2584</v>
+        <v>-13.5546</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.17</v>
       </c>
       <c r="I187" t="n">
-        <v>2.0593</v>
+        <v>1.8297</v>
       </c>
       <c r="J187" t="n">
-        <v>39.1267</v>
+        <v>34.7643</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.96</v>
       </c>
       <c r="I188" t="n">
-        <v>1.8887</v>
+        <v>1.602</v>
       </c>
       <c r="J188" t="n">
-        <v>35.8853</v>
+        <v>30.438</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.41</v>
       </c>
       <c r="I189" t="n">
-        <v>0.8178</v>
+        <v>0.9576</v>
       </c>
       <c r="J189" t="n">
-        <v>15.5382</v>
+        <v>18.1944</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.29</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5655</v>
+        <v>0.6969</v>
       </c>
       <c r="J190" t="n">
-        <v>10.7445</v>
+        <v>13.2411</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.09</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0936</v>
+        <v>0.1913</v>
       </c>
       <c r="J191" t="n">
-        <v>1.7784</v>
+        <v>3.6347</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8154</v>
+        <v>0.8286</v>
       </c>
       <c r="J192" t="n">
-        <v>22.0158</v>
+        <v>22.3722</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.28</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7381</v>
       </c>
       <c r="J193" t="n">
-        <v>19.3914</v>
+        <v>19.9287</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.22</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5435</v>
+        <v>0.6015</v>
       </c>
       <c r="J194" t="n">
-        <v>14.6745</v>
+        <v>16.2405</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.21</v>
       </c>
       <c r="I195" t="n">
-        <v>0.516</v>
+        <v>0.5779</v>
       </c>
       <c r="J195" t="n">
-        <v>13.932</v>
+        <v>15.6033</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.17</v>
       </c>
       <c r="I196" t="n">
-        <v>0.4091</v>
+        <v>0.4797</v>
       </c>
       <c r="J196" t="n">
-        <v>11.0457</v>
+        <v>12.9519</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3571</v>
+        <v>0.3953</v>
       </c>
       <c r="J197" t="n">
-        <v>9.6417</v>
+        <v>10.6731</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.07</v>
       </c>
       <c r="I198" t="n">
-        <v>0.21</v>
+        <v>0.2086</v>
       </c>
       <c r="J198" t="n">
-        <v>5.67</v>
+        <v>5.6322</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.97</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0352</v>
+        <v>-0.0419</v>
       </c>
       <c r="J199" t="n">
-        <v>-0.9504</v>
+        <v>-1.1313</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.92</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1409</v>
+        <v>-0.1035</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.8043</v>
+        <v>-2.7945</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.43</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.8335</v>
+        <v>-0.5733</v>
       </c>
       <c r="J201" t="n">
-        <v>-22.5045</v>
+        <v>-15.4791</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.71</v>
       </c>
       <c r="I202" t="n">
-        <v>1.5869</v>
+        <v>1.3833</v>
       </c>
       <c r="J202" t="n">
-        <v>47.607</v>
+        <v>41.499</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.35</v>
       </c>
       <c r="I203" t="n">
-        <v>0.865</v>
+        <v>0.8871</v>
       </c>
       <c r="J203" t="n">
-        <v>25.95</v>
+        <v>26.613</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.27</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6548</v>
+        <v>0.7106</v>
       </c>
       <c r="J204" t="n">
-        <v>19.644</v>
+        <v>21.318</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.21</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4947</v>
+        <v>0.5713</v>
       </c>
       <c r="J205" t="n">
-        <v>14.841</v>
+        <v>17.139</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.83</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6753</v>
+        <v>-0.6138</v>
       </c>
       <c r="J206" t="n">
-        <v>-20.259</v>
+        <v>-18.414</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.14</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3213</v>
+        <v>0.3503</v>
       </c>
       <c r="J207" t="n">
-        <v>9.638999999999999</v>
+        <v>10.509</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.96</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.057</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.926</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.91</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1777</v>
+        <v>-0.1153</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.331</v>
+        <v>-3.459</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.86</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2686</v>
+        <v>-0.1687</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.058</v>
+        <v>-5.061</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.75</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4361</v>
+        <v>-0.2791</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.083</v>
+        <v>-8.372999999999999</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.37</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0125</v>
+        <v>0.989</v>
       </c>
       <c r="J212" t="n">
-        <v>41.5125</v>
+        <v>40.549</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.18</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5646</v>
+        <v>0.5374</v>
       </c>
       <c r="J213" t="n">
-        <v>23.1486</v>
+        <v>22.0334</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.1133</v>
       </c>
       <c r="J214" t="n">
-        <v>2.9889</v>
+        <v>4.6453</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.98</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1744</v>
+        <v>-0.1145</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.1504</v>
+        <v>-4.6945</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.86</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5457</v>
+        <v>-0.4855</v>
       </c>
       <c r="J216" t="n">
-        <v>-22.3737</v>
+        <v>-19.9055</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.28</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4629</v>
+        <v>0.552</v>
       </c>
       <c r="J217" t="n">
-        <v>18.9789</v>
+        <v>22.632</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.21</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3654</v>
+        <v>0.4309</v>
       </c>
       <c r="J218" t="n">
-        <v>14.9814</v>
+        <v>17.6669</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3359</v>
+        <v>0.3953</v>
       </c>
       <c r="J219" t="n">
-        <v>13.7719</v>
+        <v>16.2073</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.02</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0156</v>
+        <v>0.0524</v>
       </c>
       <c r="J220" t="n">
-        <v>0.6395999999999999</v>
+        <v>2.1484</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.77</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4439</v>
+        <v>-0.2791</v>
       </c>
       <c r="J221" t="n">
-        <v>-18.1999</v>
+        <v>-11.4431</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3425/event_3425_evp_summary.xlsx
+++ b/database/event/3425/event_3425_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.5552</v>
+        <v>6.7669</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6901</v>
+        <v>0.7123</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3213</v>
+        <v>2.4562</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5552</v>
+        <v>6.7669</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0139</v>
+        <v>4.0632</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5413</v>
+        <v>2.7037</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6563</v>
+        <v>8.512</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5009</v>
+        <v>4.5964</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5413</v>
+        <v>2.7037</v>
       </c>
       <c r="K2" t="n">
         <v>99</v>
@@ -529,7 +529,7 @@
         <v>97</v>
       </c>
       <c r="M2" t="n">
-        <v>7.042199999999999</v>
+        <v>7.3001</v>
       </c>
       <c r="N2" t="n">
         <v>196</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0014</v>
+        <v>6.127</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6318</v>
+        <v>0.645</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0713</v>
+        <v>2.1649</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0014</v>
+        <v>6.127</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8964</v>
+        <v>3.8714</v>
       </c>
       <c r="G3" t="n">
-        <v>2.105</v>
+        <v>2.2556</v>
       </c>
       <c r="H3" t="n">
-        <v>8.2423</v>
+        <v>7.879</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2856</v>
+        <v>4.2546</v>
       </c>
       <c r="J3" t="n">
-        <v>2.105</v>
+        <v>2.2556</v>
       </c>
       <c r="K3" t="n">
         <v>99</v>
@@ -575,7 +575,7 @@
         <v>97</v>
       </c>
       <c r="M3" t="n">
-        <v>6.390599999999999</v>
+        <v>6.510199999999999</v>
       </c>
       <c r="N3" t="n">
         <v>196</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1805</v>
+        <v>5.1823</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5453</v>
+        <v>0.5455</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7007</v>
+        <v>1.7349</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1805</v>
+        <v>5.1823</v>
       </c>
       <c r="F4" t="n">
-        <v>2.497</v>
+        <v>3.3978</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6835</v>
+        <v>1.7845</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3114</v>
+        <v>6.3164</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7218</v>
+        <v>3.4108</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6835</v>
+        <v>1.7845</v>
       </c>
       <c r="K4" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="L4" t="n">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4053</v>
+        <v>5.1953</v>
       </c>
       <c r="N4" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0937</v>
+        <v>5.1086</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5362</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6615</v>
+        <v>1.7013</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0937</v>
+        <v>5.1086</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4476</v>
+        <v>2.4236</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6461</v>
+        <v>2.685</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6608</v>
+        <v>3.1023</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4633</v>
+        <v>1.6752</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6461</v>
+        <v>2.685</v>
       </c>
       <c r="K5" t="n">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="L5" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1094</v>
+        <v>4.3602</v>
       </c>
       <c r="N5" t="n">
-        <v>196</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9977</v>
+        <v>4.9956</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5261</v>
+        <v>0.5259</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6182</v>
+        <v>1.6499</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9977</v>
+        <v>4.9956</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5258</v>
+        <v>2.425</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4719</v>
+        <v>2.5706</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4132</v>
+        <v>3.1069</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7747</v>
+        <v>1.6777</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4719</v>
+        <v>2.5706</v>
       </c>
       <c r="K6" t="n">
         <v>54</v>
@@ -713,7 +713,7 @@
         <v>130</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2466</v>
+        <v>4.2483</v>
       </c>
       <c r="N6" t="n">
         <v>184</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6262</v>
+        <v>4.6614</v>
       </c>
       <c r="C7" t="n">
-        <v>0.487</v>
+        <v>0.4907</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4505</v>
+        <v>1.4978</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6262</v>
+        <v>4.6614</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5976</v>
+        <v>2.5384</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0286</v>
+        <v>2.123</v>
       </c>
       <c r="H7" t="n">
-        <v>3.666</v>
+        <v>3.4808</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9061</v>
+        <v>1.8796</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0286</v>
+        <v>2.123</v>
       </c>
       <c r="K7" t="n">
         <v>54</v>
@@ -759,7 +759,7 @@
         <v>130</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9347</v>
+        <v>4.0026</v>
       </c>
       <c r="N7" t="n">
         <v>184</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1466</v>
+        <v>4.1697</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4365</v>
+        <v>0.4389</v>
       </c>
       <c r="D8" t="n">
-        <v>1.234</v>
+        <v>1.2739</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1466</v>
+        <v>4.1697</v>
       </c>
       <c r="F8" t="n">
-        <v>4.0676</v>
+        <v>4.0121</v>
       </c>
       <c r="G8" t="n">
-        <v>0.079</v>
+        <v>0.1576</v>
       </c>
       <c r="H8" t="n">
-        <v>8.8452</v>
+        <v>8.343299999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5991</v>
+        <v>4.5053</v>
       </c>
       <c r="J8" t="n">
-        <v>0.079</v>
+        <v>0.1576</v>
       </c>
       <c r="K8" t="n">
         <v>99</v>
@@ -805,7 +805,7 @@
         <v>97</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6781</v>
+        <v>4.6629</v>
       </c>
       <c r="N8" t="n">
         <v>196</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0678</v>
+        <v>2.8781</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3229</v>
+        <v>0.303</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7469</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0678</v>
+        <v>2.8781</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1818</v>
+        <v>1.9467</v>
       </c>
       <c r="G9" t="n">
-        <v>0.886</v>
+        <v>0.9314</v>
       </c>
       <c r="H9" t="n">
-        <v>2.201</v>
+        <v>1.9467</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1444</v>
+        <v>1.0512</v>
       </c>
       <c r="J9" t="n">
-        <v>0.886</v>
+        <v>0.9314</v>
       </c>
       <c r="K9" t="n">
         <v>149</v>
@@ -851,7 +851,7 @@
         <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0304</v>
+        <v>1.9826</v>
       </c>
       <c r="N9" t="n">
         <v>226</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7246</v>
+        <v>2.654</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2868</v>
+        <v>0.2794</v>
       </c>
       <c r="D10" t="n">
-        <v>0.592</v>
+        <v>0.584</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7246</v>
+        <v>2.654</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7089</v>
+        <v>2.6412</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0157</v>
+        <v>0.0128</v>
       </c>
       <c r="H10" t="n">
-        <v>4.0582</v>
+        <v>3.8202</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1101</v>
+        <v>2.0629</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0157</v>
+        <v>0.0128</v>
       </c>
       <c r="K10" t="n">
         <v>149</v>
@@ -897,7 +897,7 @@
         <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1258</v>
+        <v>2.0757</v>
       </c>
       <c r="N10" t="n">
         <v>226</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6747</v>
+        <v>2.4501</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2816</v>
+        <v>0.2579</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5695</v>
+        <v>0.4911</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6747</v>
+        <v>2.4501</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6747</v>
+        <v>2.4501</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6747</v>
+        <v>2.6376</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7847</v>
+        <v>2.7056</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7847</v>
+        <v>2.7056</v>
       </c>
       <c r="N11" t="n">
         <v>162</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2718</v>
+        <v>2.3605</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2391</v>
+        <v>0.2485</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3876</v>
+        <v>0.4503</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2718</v>
+        <v>2.3605</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2718</v>
+        <v>2.0915</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2718</v>
+        <v>2.0915</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2718</v>
+        <v>1.1294</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="K12" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2718</v>
+        <v>1.3984</v>
       </c>
       <c r="N12" t="n">
-        <v>83</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2566</v>
+        <v>2.3178</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2375</v>
+        <v>0.244</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3807</v>
+        <v>0.4309</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2566</v>
+        <v>2.3178</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0579</v>
+        <v>2.3178</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1987</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0579</v>
+        <v>2.3481</v>
       </c>
       <c r="I13" t="n">
-        <v>1.07</v>
+        <v>2.3481</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1987</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="L13" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2687</v>
+        <v>2.3481</v>
       </c>
       <c r="N13" t="n">
-        <v>196</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.235</v>
+        <v>2.1638</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2353</v>
+        <v>0.2278</v>
       </c>
       <c r="D14" t="n">
-        <v>0.371</v>
+        <v>0.3608</v>
       </c>
       <c r="E14" t="n">
-        <v>2.235</v>
+        <v>2.1638</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6903</v>
+        <v>2.622</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4553</v>
+        <v>-0.4582</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9925</v>
+        <v>3.7567</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0759</v>
+        <v>2.0286</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4553</v>
+        <v>-0.4582</v>
       </c>
       <c r="K14" t="n">
         <v>149</v>
@@ -1081,7 +1081,7 @@
         <v>77</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6206</v>
+        <v>1.5704</v>
       </c>
       <c r="N14" t="n">
         <v>226</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0197</v>
+        <v>2.0275</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2126</v>
+        <v>0.2134</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2738</v>
+        <v>0.2988</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0197</v>
+        <v>2.0275</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9155</v>
+        <v>0.8609</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1042</v>
+        <v>1.1666</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9155</v>
+        <v>0.8609</v>
       </c>
       <c r="I15" t="n">
-        <v>0.476</v>
+        <v>0.4649</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1042</v>
+        <v>1.1666</v>
       </c>
       <c r="K15" t="n">
         <v>54</v>
@@ -1127,7 +1127,7 @@
         <v>130</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5802</v>
+        <v>1.6315</v>
       </c>
       <c r="N15" t="n">
         <v>184</v>
@@ -1136,81 +1136,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9372</v>
+        <v>1.8653</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2039</v>
+        <v>0.1964</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2365</v>
+        <v>0.2249</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9372</v>
+        <v>1.8653</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5443</v>
+        <v>0.467</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6071</v>
+        <v>1.3983</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4784</v>
+        <v>0.467</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8086</v>
+        <v>0.2522</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6071</v>
+        <v>1.3983</v>
       </c>
       <c r="K16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L16" t="n">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2015</v>
+        <v>1.6505</v>
       </c>
       <c r="N16" t="n">
-        <v>95</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8731</v>
+        <v>1.828</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1972</v>
+        <v>0.1924</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2076</v>
+        <v>0.2079</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8731</v>
+        <v>1.828</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4703</v>
+        <v>2.4738</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5972</v>
+        <v>-0.6458</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2176</v>
+        <v>3.2676</v>
       </c>
       <c r="I17" t="n">
-        <v>1.673</v>
+        <v>1.7645</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5972</v>
+        <v>-0.6458</v>
       </c>
       <c r="K17" t="n">
         <v>51</v>
@@ -1219,7 +1219,7 @@
         <v>44</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0758</v>
+        <v>1.1187</v>
       </c>
       <c r="N17" t="n">
         <v>95</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7401</v>
+        <v>1.7765</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1832</v>
+        <v>0.187</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1476</v>
+        <v>0.1845</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7401</v>
+        <v>1.7765</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4843</v>
+        <v>2.4016</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2558</v>
+        <v>-0.6251</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4843</v>
+        <v>3.0297</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2518</v>
+        <v>1.636</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2558</v>
+        <v>-0.6251</v>
       </c>
       <c r="K18" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L18" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5076</v>
+        <v>1.0109</v>
       </c>
       <c r="N18" t="n">
-        <v>184</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7093</v>
+        <v>1.7214</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1799</v>
+        <v>0.1812</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1336</v>
+        <v>0.1594</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7093</v>
+        <v>1.7214</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7093</v>
+        <v>1.7214</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7093</v>
+        <v>1.7214</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7796</v>
+        <v>1.7658</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7796</v>
+        <v>1.7658</v>
       </c>
       <c r="N19" t="n">
         <v>162</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>freddieb</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5099</v>
+        <v>1.4245</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1589</v>
+        <v>0.15</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0436</v>
+        <v>0.0243</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5099</v>
+        <v>1.4245</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8238</v>
+        <v>1.4245</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3139</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8238</v>
+        <v>1.4245</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9483</v>
+        <v>1.4612</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3139</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="L20" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6344000000000001</v>
+        <v>1.4612</v>
       </c>
       <c r="N20" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5082</v>
+        <v>1.4223</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1588</v>
+        <v>0.1497</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0429</v>
+        <v>0.0233</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5082</v>
+        <v>1.4223</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5082</v>
+        <v>1.4223</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5082</v>
+        <v>1.4223</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5702</v>
+        <v>1.459</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5702</v>
+        <v>1.459</v>
       </c>
       <c r="N21" t="n">
         <v>162</v>
@@ -1412,47 +1412,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>freddieb</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.5063</v>
+        <v>1.3825</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1586</v>
+        <v>0.1455</v>
       </c>
       <c r="D22" t="n">
-        <v>0.042</v>
+        <v>0.0051</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5063</v>
+        <v>1.3825</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5063</v>
+        <v>1.7358</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.3533</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5063</v>
+        <v>1.7358</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5682</v>
+        <v>0.9373</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.3533</v>
       </c>
       <c r="K22" t="n">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M22" t="n">
-        <v>1.5682</v>
+        <v>0.5840000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>162</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.488</v>
+        <v>1.3766</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1566</v>
+        <v>0.1449</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0337</v>
+        <v>0.0025</v>
       </c>
       <c r="E23" t="n">
-        <v>1.488</v>
+        <v>1.3766</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3004</v>
+        <v>2.2185</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8124</v>
+        <v>-0.8419</v>
       </c>
       <c r="H23" t="n">
-        <v>2.6189</v>
+        <v>2.4256</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3617</v>
+        <v>1.3098</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8124</v>
+        <v>-0.8419</v>
       </c>
       <c r="K23" t="n">
         <v>51</v>
@@ -1495,7 +1495,7 @@
         <v>44</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5492999999999999</v>
+        <v>0.4679000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>95</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6035</v>
+        <v>0.6062</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0635</v>
+        <v>0.0638</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3656</v>
+        <v>-0.3482</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6035</v>
+        <v>0.6062</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6035</v>
+        <v>0.6062</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6035</v>
+        <v>0.6062</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6035</v>
+        <v>0.6062</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6035</v>
+        <v>0.6062</v>
       </c>
       <c r="N24" t="n">
         <v>92</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2844</v>
+        <v>0.2352</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0299</v>
+        <v>0.0248</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.5171</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2844</v>
+        <v>0.2352</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2844</v>
+        <v>0.2352</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2844</v>
+        <v>0.2352</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2844</v>
+        <v>0.2352</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2844</v>
+        <v>0.2352</v>
       </c>
       <c r="N25" t="n">
         <v>83</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2159</v>
+        <v>0.2269</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0227</v>
+        <v>0.0239</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5405</v>
+        <v>-0.5209</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2159</v>
+        <v>0.2269</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2159</v>
+        <v>0.2269</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2159</v>
+        <v>0.2269</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2159</v>
+        <v>0.2269</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2159</v>
+        <v>0.2269</v>
       </c>
       <c r="N26" t="n">
         <v>83</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1605</v>
+        <v>0.1515</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0169</v>
+        <v>0.0159</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5656</v>
+        <v>-0.5552</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1605</v>
+        <v>0.1515</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1605</v>
+        <v>0.1515</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1605</v>
+        <v>0.1515</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1605</v>
+        <v>0.1515</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1605</v>
+        <v>0.1515</v>
       </c>
       <c r="N27" t="n">
         <v>92</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1578</v>
+        <v>0.1491</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0166</v>
+        <v>0.0157</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5668</v>
+        <v>-0.5563</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1578</v>
+        <v>0.1491</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1578</v>
+        <v>0.1491</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1578</v>
+        <v>0.1491</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1578</v>
+        <v>0.1491</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1578</v>
+        <v>0.1491</v>
       </c>
       <c r="N28" t="n">
         <v>92</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1332</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>0.014</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5779</v>
+        <v>-0.5815</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1332</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1332</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1332</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1332</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1332</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="N29" t="n">
         <v>92</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0948</v>
+        <v>0.0362</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01</v>
+        <v>0.0038</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5952</v>
+        <v>-0.6077</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0948</v>
+        <v>0.0362</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0948</v>
+        <v>0.0362</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0948</v>
+        <v>0.0362</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0948</v>
+        <v>0.0362</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0948</v>
+        <v>0.0362</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Pollo</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0969</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0009</v>
+        <v>-0.0102</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.642</v>
+        <v>-0.6683</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0969</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0969</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0969</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0969</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0969</v>
       </c>
       <c r="N31" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pollo</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0762</v>
+        <v>-0.1027</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.008</v>
+        <v>-0.0108</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6724</v>
+        <v>-0.671</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0762</v>
+        <v>-0.1027</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0762</v>
+        <v>-0.1027</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0762</v>
+        <v>-0.1027</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0762</v>
+        <v>-0.1027</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0762</v>
+        <v>-0.1027</v>
       </c>
       <c r="N32" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2776</v>
+        <v>-0.2778</v>
       </c>
       <c r="C33" t="n">
         <v>-0.0292</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7633</v>
+        <v>-0.7507</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2776</v>
+        <v>-0.2778</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0789</v>
+        <v>0.1161</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.3565</v>
+        <v>-0.3939</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0789</v>
+        <v>0.1161</v>
       </c>
       <c r="I33" t="n">
-        <v>0.041</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.3565</v>
+        <v>-0.3939</v>
       </c>
       <c r="K33" t="n">
         <v>51</v>
@@ -1955,7 +1955,7 @@
         <v>44</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3155</v>
+        <v>-0.3311999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>95</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3675</v>
+        <v>-0.349</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0387</v>
+        <v>-0.0367</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7831</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3675</v>
+        <v>-0.349</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5085</v>
+        <v>-0.4982</v>
       </c>
       <c r="G34" t="n">
-        <v>0.141</v>
+        <v>0.1492</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5085</v>
+        <v>-0.4982</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2644</v>
+        <v>-0.269</v>
       </c>
       <c r="J34" t="n">
-        <v>0.141</v>
+        <v>0.1492</v>
       </c>
       <c r="K34" t="n">
         <v>149</v>
@@ -2001,7 +2001,7 @@
         <v>77</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1234</v>
+        <v>-0.1198</v>
       </c>
       <c r="N34" t="n">
         <v>226</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3683</v>
+        <v>-0.4507</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0388</v>
+        <v>-0.0474</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8043</v>
+        <v>-0.8294</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3683</v>
+        <v>-0.4507</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3683</v>
+        <v>-0.4507</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3683</v>
+        <v>-0.4507</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3683</v>
+        <v>-0.4507</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3683</v>
+        <v>-0.4507</v>
       </c>
       <c r="N35" t="n">
         <v>70</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5607</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.059</v>
+        <v>-0.0638</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8911</v>
+        <v>-0.9002</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5607</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5607</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5607</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5607</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5607</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>70</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.7847</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9864000000000001</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.7847</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.7847</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.7847</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.7847</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.7847</v>
       </c>
       <c r="N37" t="n">
         <v>83</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0607</v>
+        <v>-1.0191</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1117</v>
+        <v>-0.1073</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1169</v>
+        <v>-1.0881</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0607</v>
+        <v>-1.0191</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0607</v>
+        <v>-1.0191</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0607</v>
+        <v>-1.0191</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1043</v>
+        <v>-1.0454</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1043</v>
+        <v>-1.0454</v>
       </c>
       <c r="N38" t="n">
         <v>162</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1687</v>
+        <v>-1.1841</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.123</v>
+        <v>-0.1246</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1656</v>
+        <v>-1.1632</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1687</v>
+        <v>-1.1841</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1687</v>
+        <v>-1.1841</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1687</v>
+        <v>-1.1841</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1687</v>
+        <v>-1.1841</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1687</v>
+        <v>-1.1841</v>
       </c>
       <c r="N39" t="n">
         <v>70</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2408</v>
+        <v>-1.2814</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1306</v>
+        <v>-0.1349</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1982</v>
+        <v>-1.2075</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2408</v>
+        <v>-1.2814</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2408</v>
+        <v>-1.2814</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2408</v>
+        <v>-1.2814</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2408</v>
+        <v>-1.2814</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2408</v>
+        <v>-1.2814</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.5459</v>
+        <v>-1.4963</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1627</v>
+        <v>-0.1575</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3359</v>
+        <v>-1.3053</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5459</v>
+        <v>-1.4963</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.0445</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5014</v>
+        <v>-0.5291</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.0445</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5431</v>
+        <v>-0.5223</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5014</v>
+        <v>-0.5291</v>
       </c>
       <c r="K41" t="n">
         <v>149</v>
@@ -2323,7 +2323,7 @@
         <v>77</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.0445</v>
+        <v>-1.0514</v>
       </c>
       <c r="N41" t="n">
         <v>226</v>
@@ -2429,10 +2429,10 @@
         <v>1.36</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9277</v>
+        <v>0.8716</v>
       </c>
       <c r="J2" t="n">
-        <v>25.9756</v>
+        <v>24.4048</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.28</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7463</v>
+        <v>0.7116</v>
       </c>
       <c r="J3" t="n">
-        <v>20.8964</v>
+        <v>19.9248</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6298</v>
+        <v>0.608</v>
       </c>
       <c r="J4" t="n">
-        <v>17.6344</v>
+        <v>17.024</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.08</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2439</v>
+        <v>0.256</v>
       </c>
       <c r="J5" t="n">
-        <v>6.8292</v>
+        <v>7.168</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.07</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2139</v>
+        <v>0.228</v>
       </c>
       <c r="J6" t="n">
-        <v>5.9892</v>
+        <v>6.384</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5282</v>
+        <v>0.5065</v>
       </c>
       <c r="J7" t="n">
-        <v>14.7896</v>
+        <v>14.182</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1432</v>
+        <v>-0.1594</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.0096</v>
+        <v>-4.4632</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.84</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1834</v>
+        <v>-0.2004</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.1352</v>
+        <v>-5.6112</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3014</v>
+        <v>-0.3168</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.4392</v>
+        <v>-8.8704</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3205</v>
+        <v>-0.3353</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.974</v>
+        <v>-9.388400000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.41</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0339</v>
+        <v>0.9825</v>
       </c>
       <c r="J12" t="n">
-        <v>25.8475</v>
+        <v>24.5625</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7137</v>
+        <v>0.68</v>
       </c>
       <c r="J13" t="n">
-        <v>17.8425</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.23</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6418</v>
+        <v>0.6163</v>
       </c>
       <c r="J14" t="n">
-        <v>16.045</v>
+        <v>15.4075</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.07</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2265</v>
+        <v>0.2367</v>
       </c>
       <c r="J15" t="n">
-        <v>5.6625</v>
+        <v>5.9175</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.79</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6891</v>
+        <v>-0.64</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.2275</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.26</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5491</v>
+        <v>0.535</v>
       </c>
       <c r="J17" t="n">
-        <v>13.7275</v>
+        <v>13.375</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4406</v>
+        <v>0.4351</v>
       </c>
       <c r="J18" t="n">
-        <v>11.015</v>
+        <v>10.8775</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2882</v>
+        <v>0.2921</v>
       </c>
       <c r="J19" t="n">
-        <v>7.205</v>
+        <v>7.3025</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.72</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3165</v>
+        <v>-0.3286</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.9125</v>
+        <v>-8.215</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.67</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3638</v>
+        <v>-0.3745</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.095000000000001</v>
+        <v>-9.362500000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0325</v>
+        <v>-0.0557</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.65</v>
+        <v>-1.114</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.67</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3225</v>
+        <v>-0.3422</v>
       </c>
       <c r="J23" t="n">
-        <v>-6.45</v>
+        <v>-6.844</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.66</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3315</v>
+        <v>-0.351</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.63</v>
+        <v>-7.02</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3406</v>
+        <v>-0.3598</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.812</v>
+        <v>-7.196</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.51</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4711</v>
+        <v>-0.4834</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.422000000000001</v>
+        <v>-9.667999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.76</v>
       </c>
       <c r="I27" t="n">
-        <v>1.133</v>
+        <v>1.2488</v>
       </c>
       <c r="J27" t="n">
-        <v>22.66</v>
+        <v>24.976</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.39</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.777</v>
       </c>
       <c r="J28" t="n">
-        <v>13.902</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.36</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6575</v>
+        <v>0.7355</v>
       </c>
       <c r="J29" t="n">
-        <v>13.15</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.35</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.7215</v>
       </c>
       <c r="J30" t="n">
-        <v>12.894</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.28</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5525</v>
+        <v>0.6194</v>
       </c>
       <c r="J31" t="n">
-        <v>11.05</v>
+        <v>12.388</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>0.98</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0086</v>
+        <v>-0.0111</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2064</v>
+        <v>-0.2664</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.96</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.025</v>
+        <v>-0.0429</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6</v>
+        <v>-1.0296</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.74</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2665</v>
+        <v>-0.286</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.396</v>
+        <v>-6.864</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.66</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3413</v>
+        <v>-0.3585</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.1912</v>
+        <v>-8.603999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.42</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5647</v>
+        <v>-0.5694</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.5528</v>
+        <v>-13.6656</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.77</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1724</v>
+        <v>1.2857</v>
       </c>
       <c r="J37" t="n">
-        <v>28.1376</v>
+        <v>30.8568</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.38</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6938</v>
+        <v>0.7728</v>
       </c>
       <c r="J38" t="n">
-        <v>16.6512</v>
+        <v>18.5472</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.28</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5661</v>
+        <v>0.6312</v>
       </c>
       <c r="J39" t="n">
-        <v>13.5864</v>
+        <v>15.1488</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.08</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2192</v>
+        <v>0.2388</v>
       </c>
       <c r="J40" t="n">
-        <v>5.2608</v>
+        <v>5.7312</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.03</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0585</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>1.404</v>
+        <v>2.064</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.11</v>
       </c>
       <c r="I42" t="n">
-        <v>0.233</v>
+        <v>0.2346</v>
       </c>
       <c r="J42" t="n">
-        <v>6.757</v>
+        <v>6.8034</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0772</v>
+        <v>-0.0907</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.2388</v>
+        <v>-2.6303</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.9</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1231</v>
+        <v>-0.1385</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.5699</v>
+        <v>-4.0165</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.82</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2049</v>
+        <v>-0.2216</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.9421</v>
+        <v>-6.4264</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.65</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3694</v>
+        <v>-0.3822</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.7126</v>
+        <v>-11.0838</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.37</v>
       </c>
       <c r="I47" t="n">
-        <v>0.422</v>
+        <v>0.4785</v>
       </c>
       <c r="J47" t="n">
-        <v>12.238</v>
+        <v>13.8765</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.3</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3744</v>
+        <v>0.4151</v>
       </c>
       <c r="J48" t="n">
-        <v>10.8576</v>
+        <v>12.0379</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.24</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3288</v>
+        <v>0.3474</v>
       </c>
       <c r="J49" t="n">
-        <v>9.5352</v>
+        <v>10.0746</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0164</v>
+        <v>-0.0126</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.4756</v>
+        <v>-0.3654</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.97</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0677</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>-1.9633</v>
+        <v>-2.0851</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6496</v>
+        <v>0.7195</v>
       </c>
       <c r="J52" t="n">
-        <v>17.5392</v>
+        <v>19.4265</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.5982</v>
       </c>
       <c r="J53" t="n">
-        <v>14.5746</v>
+        <v>16.1514</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.2</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4694</v>
+        <v>0.5192</v>
       </c>
       <c r="J54" t="n">
-        <v>12.6738</v>
+        <v>14.0184</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.11</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3321</v>
+        <v>0.3397</v>
       </c>
       <c r="J55" t="n">
-        <v>8.966699999999999</v>
+        <v>9.171900000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.99</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0975</v>
+        <v>-0.0891</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.6325</v>
+        <v>-2.4057</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.17</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3689</v>
+        <v>0.3892</v>
       </c>
       <c r="J57" t="n">
-        <v>9.9603</v>
+        <v>10.5084</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.09</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2341</v>
+        <v>0.2387</v>
       </c>
       <c r="J58" t="n">
-        <v>6.3207</v>
+        <v>6.4449</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.93</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0968</v>
+        <v>-0.109</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.6136</v>
+        <v>-2.943</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.88</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1525</v>
+        <v>-0.1665</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.1175</v>
+        <v>-4.4955</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.77</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.265</v>
+        <v>-0.2788</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.155</v>
+        <v>-7.5276</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.57</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9149</v>
+        <v>1.0153</v>
       </c>
       <c r="J62" t="n">
-        <v>19.2129</v>
+        <v>21.3213</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.48</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8064</v>
+        <v>0.8982</v>
       </c>
       <c r="J63" t="n">
-        <v>16.9344</v>
+        <v>18.8622</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.39</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6976</v>
+        <v>0.7791</v>
       </c>
       <c r="J64" t="n">
-        <v>14.6496</v>
+        <v>16.3611</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.38</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6854</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>14.3934</v>
+        <v>16.0776</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.17</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3995</v>
+        <v>0.4455</v>
       </c>
       <c r="J66" t="n">
-        <v>8.3895</v>
+        <v>9.355499999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.05</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2299</v>
+        <v>0.2142</v>
       </c>
       <c r="J67" t="n">
-        <v>4.8279</v>
+        <v>4.4982</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.87</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1366</v>
+        <v>-0.1569</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.8686</v>
+        <v>-3.2949</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.72</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2855</v>
+        <v>-0.3045</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.9955</v>
+        <v>-6.3945</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.67</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3325</v>
+        <v>-0.35</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.9825</v>
+        <v>-7.35</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.47</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5191</v>
+        <v>-0.5268</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.9011</v>
+        <v>-11.0628</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.08</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3213</v>
+        <v>0.2979</v>
       </c>
       <c r="J72" t="n">
-        <v>7.0686</v>
+        <v>6.5538</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.91</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0829</v>
+        <v>-0.1044</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.8238</v>
+        <v>-2.2968</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.71</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2911</v>
+        <v>-0.3107</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.4042</v>
+        <v>-6.8354</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.57</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4215</v>
+        <v>-0.4357</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.273</v>
+        <v>-9.5854</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.36</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6168</v>
+        <v>-0.6182</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.5696</v>
+        <v>-13.6004</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.86</v>
       </c>
       <c r="I77" t="n">
-        <v>1.5173</v>
+        <v>1.5135</v>
       </c>
       <c r="J77" t="n">
-        <v>33.3806</v>
+        <v>33.297</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.83</v>
       </c>
       <c r="I78" t="n">
-        <v>1.4831</v>
+        <v>1.4775</v>
       </c>
       <c r="J78" t="n">
-        <v>32.6282</v>
+        <v>32.505</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5589</v>
+        <v>0.5544</v>
       </c>
       <c r="J79" t="n">
-        <v>12.2958</v>
+        <v>12.1968</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.19</v>
       </c>
       <c r="I80" t="n">
-        <v>0.485</v>
+        <v>0.4882</v>
       </c>
       <c r="J80" t="n">
-        <v>10.67</v>
+        <v>10.7404</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.14</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3562</v>
+        <v>0.3717</v>
       </c>
       <c r="J81" t="n">
-        <v>7.8364</v>
+        <v>8.1774</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.92</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.0267</v>
+        <v>-0.0572</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.4806</v>
+        <v>-1.0296</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.58</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.3917</v>
+        <v>-0.411</v>
       </c>
       <c r="J83" t="n">
-        <v>-7.0506</v>
+        <v>-7.398</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.4099</v>
+        <v>-0.4282</v>
       </c>
       <c r="J84" t="n">
-        <v>-7.3782</v>
+        <v>-7.7076</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.51</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4563</v>
+        <v>-0.4719</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.2134</v>
+        <v>-8.494199999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.45</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.513</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.234</v>
+        <v>-9.444599999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>2.27</v>
       </c>
       <c r="I87" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J87" t="n">
-        <v>33.0084</v>
+        <v>34.8696</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.6</v>
       </c>
       <c r="I88" t="n">
-        <v>1.2048</v>
+        <v>1.184</v>
       </c>
       <c r="J88" t="n">
-        <v>21.6864</v>
+        <v>21.312</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.43</v>
       </c>
       <c r="I89" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.954</v>
       </c>
       <c r="J89" t="n">
-        <v>17.973</v>
+        <v>17.172</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.29</v>
       </c>
       <c r="I90" t="n">
-        <v>0.7046</v>
+        <v>0.6873</v>
       </c>
       <c r="J90" t="n">
-        <v>12.6828</v>
+        <v>12.3714</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.13</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3102</v>
+        <v>0.3338</v>
       </c>
       <c r="J91" t="n">
-        <v>5.5836</v>
+        <v>6.0084</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2865</v>
+        <v>0.2942</v>
       </c>
       <c r="J92" t="n">
-        <v>7.1625</v>
+        <v>7.355</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.13</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2285</v>
+        <v>0.2381</v>
       </c>
       <c r="J93" t="n">
-        <v>5.7125</v>
+        <v>5.9525</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.07</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1358</v>
+        <v>0.1467</v>
       </c>
       <c r="J94" t="n">
-        <v>3.395</v>
+        <v>3.6675</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.91</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1263</v>
+        <v>-0.138</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.1575</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.87</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1703</v>
+        <v>-0.1828</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.2575</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6292</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>15.73</v>
+        <v>15.7375</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.41</v>
       </c>
       <c r="I98" t="n">
-        <v>0.529</v>
+        <v>0.5356</v>
       </c>
       <c r="J98" t="n">
-        <v>13.225</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.14</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2094</v>
+        <v>0.2269</v>
       </c>
       <c r="J99" t="n">
-        <v>5.235</v>
+        <v>5.6725</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.93</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1183</v>
+        <v>-0.1257</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.9575</v>
+        <v>-3.1425</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.89</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1638</v>
+        <v>-0.1727</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.095</v>
+        <v>-4.3175</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.35</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9246</v>
+        <v>0.8653</v>
       </c>
       <c r="J102" t="n">
-        <v>26.8134</v>
+        <v>25.0937</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.25</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6597</v>
       </c>
       <c r="J103" t="n">
-        <v>20.039</v>
+        <v>19.1313</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.15</v>
       </c>
       <c r="I104" t="n">
-        <v>0.446</v>
+        <v>0.4396</v>
       </c>
       <c r="J104" t="n">
-        <v>12.934</v>
+        <v>12.7484</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1651</v>
+        <v>0.1784</v>
       </c>
       <c r="J105" t="n">
-        <v>4.7879</v>
+        <v>5.1736</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2693</v>
+        <v>-0.2584</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.8097</v>
+        <v>-7.4936</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.01</v>
       </c>
       <c r="I107" t="n">
-        <v>0.0544</v>
+        <v>0.0553</v>
       </c>
       <c r="J107" t="n">
-        <v>1.5776</v>
+        <v>1.6037</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0544</v>
+        <v>0.0553</v>
       </c>
       <c r="J108" t="n">
-        <v>1.5776</v>
+        <v>1.6037</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.95</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0692</v>
+        <v>-0.081</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.0068</v>
+        <v>-2.349</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.91</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.115</v>
+        <v>-0.1292</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.335</v>
+        <v>-3.7468</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.72</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3076</v>
+        <v>-0.3216</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.920400000000001</v>
+        <v>-9.3264</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.58</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2666</v>
+        <v>1.2337</v>
       </c>
       <c r="J112" t="n">
-        <v>37.998</v>
+        <v>37.011</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.19</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5517</v>
+        <v>0.5341</v>
       </c>
       <c r="J113" t="n">
-        <v>16.551</v>
+        <v>16.023</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.09</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2917</v>
+        <v>0.296</v>
       </c>
       <c r="J114" t="n">
-        <v>8.750999999999999</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.91</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3539</v>
+        <v>-0.3389</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.617</v>
+        <v>-10.167</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5502</v>
+        <v>-0.5175</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.506</v>
+        <v>-15.525</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4893</v>
+        <v>0.4812</v>
       </c>
       <c r="J117" t="n">
-        <v>14.679</v>
+        <v>14.436</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.03</v>
       </c>
       <c r="I118" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>2.697</v>
+        <v>2.958</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.03</v>
       </c>
       <c r="I119" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>2.697</v>
+        <v>2.958</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.93</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1013</v>
+        <v>-0.1125</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.039</v>
+        <v>-3.375</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1997</v>
+        <v>-0.213</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.991</v>
+        <v>-6.39</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.02</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2116</v>
+        <v>0.1803</v>
       </c>
       <c r="J122" t="n">
-        <v>4.4436</v>
+        <v>3.7863</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.79</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2016</v>
+        <v>-0.2256</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.2336</v>
+        <v>-4.7376</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.59</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3922</v>
+        <v>-0.4097</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.2362</v>
+        <v>-8.6037</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.54</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4388</v>
+        <v>-0.4538</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.2148</v>
+        <v>-9.5298</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.37</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5987</v>
+        <v>-0.6027</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.5727</v>
+        <v>-12.6567</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.8</v>
       </c>
       <c r="I127" t="n">
-        <v>1.4319</v>
+        <v>1.4264</v>
       </c>
       <c r="J127" t="n">
-        <v>30.0699</v>
+        <v>29.9544</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.73</v>
       </c>
       <c r="I128" t="n">
-        <v>1.3529</v>
+        <v>1.3426</v>
       </c>
       <c r="J128" t="n">
-        <v>28.4109</v>
+        <v>28.1946</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.71</v>
       </c>
       <c r="I129" t="n">
-        <v>1.3303</v>
+        <v>1.3184</v>
       </c>
       <c r="J129" t="n">
-        <v>27.9363</v>
+        <v>27.6864</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.47</v>
       </c>
       <c r="I130" t="n">
-        <v>1.0551</v>
+        <v>1.0179</v>
       </c>
       <c r="J130" t="n">
-        <v>22.1571</v>
+        <v>21.3759</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1227</v>
+        <v>-0.0856</v>
       </c>
       <c r="J131" t="n">
-        <v>-2.5767</v>
+        <v>-1.7976</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I132" t="n">
-        <v>0.0809</v>
+        <v>0.0268</v>
       </c>
       <c r="J132" t="n">
-        <v>1.5371</v>
+        <v>0.5092</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.9</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0539</v>
+        <v>-0.0842</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.0241</v>
+        <v>-1.5998</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.44</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.5229</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="J134" t="n">
-        <v>-9.9351</v>
+        <v>-10.1422</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.42</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.542</v>
+        <v>-0.5515</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.298</v>
+        <v>-10.4785</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.3</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.657</v>
+        <v>-0.6572</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.483</v>
+        <v>-12.4868</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.44</v>
       </c>
       <c r="I137" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J137" t="n">
-        <v>34.8422</v>
+        <v>36.8068</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.67</v>
       </c>
       <c r="I138" t="n">
-        <v>1.2745</v>
+        <v>1.261</v>
       </c>
       <c r="J138" t="n">
-        <v>24.2155</v>
+        <v>23.959</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.63</v>
       </c>
       <c r="I139" t="n">
-        <v>1.2311</v>
+        <v>1.2141</v>
       </c>
       <c r="J139" t="n">
-        <v>23.3909</v>
+        <v>23.0679</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.32</v>
       </c>
       <c r="I140" t="n">
-        <v>0.7541</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>14.3279</v>
+        <v>13.9536</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.15</v>
       </c>
       <c r="I141" t="n">
-        <v>0.3451</v>
+        <v>0.3694</v>
       </c>
       <c r="J141" t="n">
-        <v>6.5569</v>
+        <v>7.0186</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.07</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2399</v>
+        <v>0.2327</v>
       </c>
       <c r="J142" t="n">
-        <v>5.7576</v>
+        <v>5.5848</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.01</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0843</v>
+        <v>0.0771</v>
       </c>
       <c r="J143" t="n">
-        <v>2.0232</v>
+        <v>1.8504</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.79</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2281</v>
+        <v>-0.2461</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.4744</v>
+        <v>-5.9064</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3621</v>
+        <v>-0.3765</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.6904</v>
+        <v>-9.036</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.63</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3809</v>
+        <v>-0.3945</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.1416</v>
+        <v>-9.468</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.83</v>
       </c>
       <c r="I147" t="n">
-        <v>1.4993</v>
+        <v>1.4919</v>
       </c>
       <c r="J147" t="n">
-        <v>35.9832</v>
+        <v>35.8056</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.4</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9686</v>
+        <v>0.9184</v>
       </c>
       <c r="J148" t="n">
-        <v>23.2464</v>
+        <v>22.0416</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.39</v>
       </c>
       <c r="I149" t="n">
-        <v>0.9504</v>
+        <v>0.9004</v>
       </c>
       <c r="J149" t="n">
-        <v>22.8096</v>
+        <v>21.6096</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.39</v>
       </c>
       <c r="I150" t="n">
-        <v>0.9504</v>
+        <v>0.9004</v>
       </c>
       <c r="J150" t="n">
-        <v>22.8096</v>
+        <v>21.6096</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.87</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.4854</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.6648</v>
+        <v>-11.6496</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.22</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4675</v>
+        <v>0.4619</v>
       </c>
       <c r="J152" t="n">
-        <v>12.6225</v>
+        <v>12.4713</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1997</v>
+        <v>0.2087</v>
       </c>
       <c r="J153" t="n">
-        <v>5.3919</v>
+        <v>5.6349</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.03</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0883</v>
+        <v>0.0975</v>
       </c>
       <c r="J154" t="n">
-        <v>2.3841</v>
+        <v>2.6325</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0906</v>
+        <v>-0.1009</v>
       </c>
       <c r="J155" t="n">
-        <v>-2.4462</v>
+        <v>-2.7243</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1907</v>
+        <v>-0.2036</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.1489</v>
+        <v>-5.4972</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.29</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7907</v>
+        <v>0.7467</v>
       </c>
       <c r="J157" t="n">
-        <v>21.3489</v>
+        <v>20.1609</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.28</v>
       </c>
       <c r="I158" t="n">
-        <v>0.767</v>
+        <v>0.7259</v>
       </c>
       <c r="J158" t="n">
-        <v>20.709</v>
+        <v>19.5993</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3715</v>
+        <v>0.3705</v>
       </c>
       <c r="J159" t="n">
-        <v>10.0305</v>
+        <v>10.0035</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.12</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3715</v>
+        <v>0.3705</v>
       </c>
       <c r="J160" t="n">
-        <v>10.0305</v>
+        <v>10.0035</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4991</v>
+        <v>-0.4708</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.4757</v>
+        <v>-12.7116</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.52</v>
       </c>
       <c r="I162" t="n">
-        <v>1.1505</v>
+        <v>1.1171</v>
       </c>
       <c r="J162" t="n">
-        <v>27.612</v>
+        <v>26.8104</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.35</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.839</v>
       </c>
       <c r="J163" t="n">
-        <v>21.3024</v>
+        <v>20.136</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.34</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8656</v>
+        <v>0.8196</v>
       </c>
       <c r="J164" t="n">
-        <v>20.7744</v>
+        <v>19.6704</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.19</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5229</v>
+        <v>0.5145</v>
       </c>
       <c r="J165" t="n">
-        <v>12.5496</v>
+        <v>12.348</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.96</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2346</v>
+        <v>-0.2177</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.6304</v>
+        <v>-5.2248</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.15</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3916</v>
+        <v>0.3804</v>
       </c>
       <c r="J167" t="n">
-        <v>9.398400000000001</v>
+        <v>9.1296</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2667</v>
+        <v>0.2625</v>
       </c>
       <c r="J168" t="n">
-        <v>6.4008</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1532</v>
+        <v>-0.1697</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.6768</v>
+        <v>-4.0728</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.66</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3584</v>
+        <v>-0.3719</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.601599999999999</v>
+        <v>-8.925599999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.59</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4238</v>
+        <v>-0.4344</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.1712</v>
+        <v>-10.4256</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.19</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4542</v>
+        <v>0.4415</v>
       </c>
       <c r="J172" t="n">
-        <v>10.9008</v>
+        <v>10.596</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.15</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3763</v>
+        <v>0.3692</v>
       </c>
       <c r="J173" t="n">
-        <v>9.0312</v>
+        <v>8.860799999999999</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.93</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0919</v>
+        <v>-0.1054</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.2056</v>
+        <v>-2.5296</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.64</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3818</v>
+        <v>-0.3936</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.1632</v>
+        <v>-9.446400000000001</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3911</v>
+        <v>-0.4025</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.3864</v>
+        <v>-9.66</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2307</v>
+        <v>1.2019</v>
       </c>
       <c r="J177" t="n">
-        <v>29.5368</v>
+        <v>28.8456</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.55</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1933</v>
+        <v>1.1619</v>
       </c>
       <c r="J178" t="n">
-        <v>28.6392</v>
+        <v>27.8856</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.23</v>
       </c>
       <c r="I179" t="n">
-        <v>0.6236</v>
+        <v>0.6039</v>
       </c>
       <c r="J179" t="n">
-        <v>14.9664</v>
+        <v>14.4936</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.12</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3468</v>
+        <v>0.3535</v>
       </c>
       <c r="J180" t="n">
-        <v>8.3232</v>
+        <v>8.484</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.76</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7876</v>
+        <v>-0.723</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.9024</v>
+        <v>-17.352</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I182" t="n">
-        <v>0.0837</v>
+        <v>0.0107</v>
       </c>
       <c r="J182" t="n">
-        <v>1.5903</v>
+        <v>0.2033</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.52</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.4327</v>
+        <v>-0.4521</v>
       </c>
       <c r="J183" t="n">
-        <v>-8.221299999999999</v>
+        <v>-8.5899</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.47</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.4781</v>
+        <v>-0.4947</v>
       </c>
       <c r="J184" t="n">
-        <v>-9.0839</v>
+        <v>-9.3993</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.47</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4781</v>
+        <v>-0.4947</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.0839</v>
+        <v>-9.3993</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.23</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7134</v>
+        <v>-0.7101</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.5546</v>
+        <v>-13.4919</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.17</v>
       </c>
       <c r="I187" t="n">
-        <v>1.8297</v>
+        <v>1.8449</v>
       </c>
       <c r="J187" t="n">
-        <v>34.7643</v>
+        <v>35.0531</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.96</v>
       </c>
       <c r="I188" t="n">
-        <v>1.602</v>
+        <v>1.6071</v>
       </c>
       <c r="J188" t="n">
-        <v>30.438</v>
+        <v>30.5349</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.41</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9576</v>
+        <v>0.9137</v>
       </c>
       <c r="J189" t="n">
-        <v>18.1944</v>
+        <v>17.3603</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.29</v>
       </c>
       <c r="I190" t="n">
-        <v>0.6969</v>
+        <v>0.6819</v>
       </c>
       <c r="J190" t="n">
-        <v>13.2411</v>
+        <v>12.9561</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.09</v>
       </c>
       <c r="I191" t="n">
-        <v>0.1913</v>
+        <v>0.226</v>
       </c>
       <c r="J191" t="n">
-        <v>3.6347</v>
+        <v>4.294</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8286</v>
+        <v>0.7857</v>
       </c>
       <c r="J192" t="n">
-        <v>22.3722</v>
+        <v>21.2139</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.28</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7381</v>
+        <v>0.7059</v>
       </c>
       <c r="J193" t="n">
-        <v>19.9287</v>
+        <v>19.0593</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.22</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6015</v>
+        <v>0.5838</v>
       </c>
       <c r="J194" t="n">
-        <v>16.2405</v>
+        <v>15.7626</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.21</v>
       </c>
       <c r="I195" t="n">
-        <v>0.5779</v>
+        <v>0.5626</v>
       </c>
       <c r="J195" t="n">
-        <v>15.6033</v>
+        <v>15.1902</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.17</v>
       </c>
       <c r="I196" t="n">
-        <v>0.4797</v>
+        <v>0.4741</v>
       </c>
       <c r="J196" t="n">
-        <v>12.9519</v>
+        <v>12.8007</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3953</v>
+        <v>0.387</v>
       </c>
       <c r="J197" t="n">
-        <v>10.6731</v>
+        <v>10.449</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.07</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2086</v>
+        <v>0.2098</v>
       </c>
       <c r="J198" t="n">
-        <v>5.6322</v>
+        <v>5.6646</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.97</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0419</v>
+        <v>-0.052</v>
       </c>
       <c r="J199" t="n">
-        <v>-1.1313</v>
+        <v>-1.404</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.92</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1035</v>
+        <v>-0.1174</v>
       </c>
       <c r="J200" t="n">
-        <v>-2.7945</v>
+        <v>-3.1698</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.43</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5733</v>
+        <v>-0.575</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.4791</v>
+        <v>-15.525</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.71</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3833</v>
+        <v>1.3651</v>
       </c>
       <c r="J202" t="n">
-        <v>41.499</v>
+        <v>40.953</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.35</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8871</v>
+        <v>0.8387</v>
       </c>
       <c r="J203" t="n">
-        <v>26.613</v>
+        <v>25.161</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.27</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7106</v>
+        <v>0.6826</v>
       </c>
       <c r="J204" t="n">
-        <v>21.318</v>
+        <v>20.478</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.21</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5713</v>
+        <v>0.5581</v>
       </c>
       <c r="J205" t="n">
-        <v>17.139</v>
+        <v>16.743</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.83</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6138</v>
+        <v>-0.5674</v>
       </c>
       <c r="J206" t="n">
-        <v>-18.414</v>
+        <v>-17.022</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.14</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3503</v>
+        <v>0.346</v>
       </c>
       <c r="J207" t="n">
-        <v>10.509</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.96</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.057</v>
+        <v>-0.0678</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.71</v>
+        <v>-2.034</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.91</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1153</v>
+        <v>-0.1295</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.459</v>
+        <v>-3.885</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.86</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1687</v>
+        <v>-0.1841</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.061</v>
+        <v>-5.523</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.75</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2791</v>
+        <v>-0.2938</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.372999999999999</v>
+        <v>-8.814</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.37</v>
       </c>
       <c r="I212" t="n">
-        <v>0.989</v>
+        <v>0.924</v>
       </c>
       <c r="J212" t="n">
-        <v>40.549</v>
+        <v>37.884</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.18</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5374</v>
+        <v>0.519</v>
       </c>
       <c r="J213" t="n">
-        <v>22.0334</v>
+        <v>21.279</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1133</v>
+        <v>0.1241</v>
       </c>
       <c r="J214" t="n">
-        <v>4.6453</v>
+        <v>5.0881</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.98</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1145</v>
+        <v>-0.1138</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.6945</v>
+        <v>-4.6658</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.86</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4855</v>
+        <v>-0.4613</v>
       </c>
       <c r="J216" t="n">
-        <v>-19.9055</v>
+        <v>-18.9133</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.28</v>
       </c>
       <c r="I217" t="n">
-        <v>0.552</v>
+        <v>0.5435</v>
       </c>
       <c r="J217" t="n">
-        <v>22.632</v>
+        <v>22.2835</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.21</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4309</v>
+        <v>0.4316</v>
       </c>
       <c r="J218" t="n">
-        <v>17.6669</v>
+        <v>17.6956</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3953</v>
+        <v>0.3985</v>
       </c>
       <c r="J219" t="n">
-        <v>16.2073</v>
+        <v>16.3385</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.02</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0524</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="J220" t="n">
-        <v>2.1484</v>
+        <v>2.6117</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.77</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2791</v>
+        <v>-0.2899</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.4431</v>
+        <v>-11.8859</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3425/event_3425_evp_summary.xlsx
+++ b/database/event/3425/event_3425_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7669</v>
+        <v>6.5248</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7123</v>
+        <v>0.6869</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4562</v>
+        <v>2.3666</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7669</v>
+        <v>6.5248</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0632</v>
+        <v>3.9274</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7037</v>
+        <v>2.5974</v>
       </c>
       <c r="H2" t="n">
-        <v>8.512</v>
+        <v>8.3027</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5964</v>
+        <v>4.6617</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7037</v>
+        <v>2.5974</v>
       </c>
       <c r="K2" t="n">
         <v>99</v>
@@ -529,7 +529,7 @@
         <v>97</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3001</v>
+        <v>7.2591</v>
       </c>
       <c r="N2" t="n">
         <v>196</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.127</v>
+        <v>5.9779</v>
       </c>
       <c r="C3" t="n">
-        <v>0.645</v>
+        <v>0.6293</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1649</v>
+        <v>2.1174</v>
       </c>
       <c r="E3" t="n">
-        <v>6.127</v>
+        <v>5.9779</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8714</v>
+        <v>3.7721</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2556</v>
+        <v>2.2058</v>
       </c>
       <c r="H3" t="n">
-        <v>7.879</v>
+        <v>7.7196</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2546</v>
+        <v>4.3343</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2556</v>
+        <v>2.2058</v>
       </c>
       <c r="K3" t="n">
         <v>99</v>
@@ -575,7 +575,7 @@
         <v>97</v>
       </c>
       <c r="M3" t="n">
-        <v>6.510199999999999</v>
+        <v>6.5401</v>
       </c>
       <c r="N3" t="n">
         <v>196</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1823</v>
+        <v>5.1108</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5455</v>
+        <v>0.538</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7349</v>
+        <v>1.7224</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1823</v>
+        <v>5.1108</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3978</v>
+        <v>2.5022</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7845</v>
+        <v>2.6086</v>
       </c>
       <c r="H4" t="n">
-        <v>6.3164</v>
+        <v>2.9515</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4108</v>
+        <v>1.6572</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7845</v>
+        <v>2.6086</v>
       </c>
       <c r="K4" t="n">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="L4" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="M4" t="n">
-        <v>5.1953</v>
+        <v>4.2658</v>
       </c>
       <c r="N4" t="n">
-        <v>196</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1086</v>
+        <v>5.0626</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5329</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7013</v>
+        <v>1.7005</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1086</v>
+        <v>5.0626</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4236</v>
+        <v>3.3375</v>
       </c>
       <c r="G5" t="n">
-        <v>2.685</v>
+        <v>1.7251</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1023</v>
+        <v>6.0878</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6752</v>
+        <v>3.4181</v>
       </c>
       <c r="J5" t="n">
-        <v>2.685</v>
+        <v>1.7251</v>
       </c>
       <c r="K5" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="L5" t="n">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3602</v>
+        <v>5.1432</v>
       </c>
       <c r="N5" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9956</v>
+        <v>5.0172</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5259</v>
+        <v>0.5282</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6499</v>
+        <v>1.6798</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9956</v>
+        <v>5.0172</v>
       </c>
       <c r="F6" t="n">
-        <v>2.425</v>
+        <v>2.4939</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5706</v>
+        <v>2.5233</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1069</v>
+        <v>2.9207</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6777</v>
+        <v>1.6399</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5706</v>
+        <v>2.5233</v>
       </c>
       <c r="K6" t="n">
         <v>54</v>
@@ -713,7 +713,7 @@
         <v>130</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2483</v>
+        <v>4.1632</v>
       </c>
       <c r="N6" t="n">
         <v>184</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6614</v>
+        <v>4.612</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4907</v>
+        <v>0.4855</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4978</v>
+        <v>1.4952</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6614</v>
+        <v>4.612</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5384</v>
+        <v>2.6039</v>
       </c>
       <c r="G7" t="n">
-        <v>2.123</v>
+        <v>2.0081</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4808</v>
+        <v>3.3334</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8796</v>
+        <v>1.8716</v>
       </c>
       <c r="J7" t="n">
-        <v>2.123</v>
+        <v>2.0081</v>
       </c>
       <c r="K7" t="n">
         <v>54</v>
@@ -759,7 +759,7 @@
         <v>130</v>
       </c>
       <c r="M7" t="n">
-        <v>4.0026</v>
+        <v>3.8797</v>
       </c>
       <c r="N7" t="n">
         <v>184</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1697</v>
+        <v>4.0544</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4389</v>
+        <v>0.4268</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2739</v>
+        <v>1.2412</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1697</v>
+        <v>4.0544</v>
       </c>
       <c r="F8" t="n">
-        <v>4.0121</v>
+        <v>3.893</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1576</v>
+        <v>0.1614</v>
       </c>
       <c r="H8" t="n">
-        <v>8.343299999999999</v>
+        <v>8.173400000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5053</v>
+        <v>4.5891</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1576</v>
+        <v>0.1614</v>
       </c>
       <c r="K8" t="n">
         <v>99</v>
@@ -805,7 +805,7 @@
         <v>97</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6629</v>
+        <v>4.750500000000001</v>
       </c>
       <c r="N8" t="n">
         <v>196</v>
@@ -814,35 +814,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8781</v>
+        <v>2.5964</v>
       </c>
       <c r="C9" t="n">
-        <v>0.303</v>
+        <v>0.2733</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.577</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8781</v>
+        <v>2.5964</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9467</v>
+        <v>2.6091</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9314</v>
+        <v>-0.0127</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9467</v>
+        <v>3.353</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0512</v>
+        <v>1.8826</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9314</v>
+        <v>-0.0127</v>
       </c>
       <c r="K9" t="n">
         <v>149</v>
@@ -851,7 +851,7 @@
         <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9826</v>
+        <v>1.8699</v>
       </c>
       <c r="N9" t="n">
         <v>226</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.654</v>
+        <v>2.583</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2794</v>
+        <v>0.2719</v>
       </c>
       <c r="D10" t="n">
-        <v>0.584</v>
+        <v>0.5709</v>
       </c>
       <c r="E10" t="n">
-        <v>2.654</v>
+        <v>2.583</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6412</v>
+        <v>1.7846</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0128</v>
+        <v>0.7984</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8202</v>
+        <v>1.7846</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0629</v>
+        <v>1.002</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0128</v>
+        <v>0.7984</v>
       </c>
       <c r="K10" t="n">
         <v>149</v>
@@ -897,7 +897,7 @@
         <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0757</v>
+        <v>1.8004</v>
       </c>
       <c r="N10" t="n">
         <v>226</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4501</v>
+        <v>2.3417</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2579</v>
+        <v>0.2465</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4911</v>
+        <v>0.461</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4501</v>
+        <v>2.3417</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4501</v>
+        <v>2.3417</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6376</v>
+        <v>2.4162</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7056</v>
+        <v>2.4808</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7056</v>
+        <v>2.4808</v>
       </c>
       <c r="N11" t="n">
         <v>162</v>
@@ -952,139 +952,139 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3605</v>
+        <v>2.312</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2485</v>
+        <v>0.2434</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4503</v>
+        <v>0.4474</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3605</v>
+        <v>2.312</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0915</v>
+        <v>2.312</v>
       </c>
       <c r="G12" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0915</v>
+        <v>2.3483</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1294</v>
+        <v>2.3483</v>
       </c>
       <c r="J12" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="L12" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3984</v>
+        <v>2.3483</v>
       </c>
       <c r="N12" t="n">
-        <v>196</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3178</v>
+        <v>2.143</v>
       </c>
       <c r="C13" t="n">
-        <v>0.244</v>
+        <v>0.2256</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4309</v>
+        <v>0.3705</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3178</v>
+        <v>2.143</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3178</v>
+        <v>2.6423</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.4993</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3481</v>
+        <v>3.4778</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3481</v>
+        <v>1.9527</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.4993</v>
       </c>
       <c r="K13" t="n">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3481</v>
+        <v>1.4534</v>
       </c>
       <c r="N13" t="n">
-        <v>83</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1638</v>
+        <v>2.1302</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2278</v>
+        <v>0.2242</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3608</v>
+        <v>0.3646</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1638</v>
+        <v>2.1302</v>
       </c>
       <c r="F14" t="n">
-        <v>2.622</v>
+        <v>1.8687</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4582</v>
+        <v>0.2615</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7567</v>
+        <v>1.8687</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0286</v>
+        <v>1.0492</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4582</v>
+        <v>0.2615</v>
       </c>
       <c r="K14" t="n">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="L14" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5704</v>
+        <v>1.3107</v>
       </c>
       <c r="N14" t="n">
-        <v>226</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0275</v>
+        <v>1.9647</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2134</v>
+        <v>0.2068</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2988</v>
+        <v>0.2892</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0275</v>
+        <v>1.9647</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8609</v>
+        <v>0.8396</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1666</v>
+        <v>1.1251</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8609</v>
+        <v>0.8396</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4649</v>
+        <v>0.4714</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1666</v>
+        <v>1.1251</v>
       </c>
       <c r="K15" t="n">
         <v>54</v>
@@ -1127,7 +1127,7 @@
         <v>130</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6315</v>
+        <v>1.5965</v>
       </c>
       <c r="N15" t="n">
         <v>184</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8653</v>
+        <v>1.9275</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1964</v>
+        <v>0.2029</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2249</v>
+        <v>0.2723</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8653</v>
+        <v>1.9275</v>
       </c>
       <c r="F16" t="n">
-        <v>0.467</v>
+        <v>2.545</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3983</v>
+        <v>-0.6175</v>
       </c>
       <c r="H16" t="n">
-        <v>0.467</v>
+        <v>3.1126</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2522</v>
+        <v>1.7476</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3983</v>
+        <v>-0.6175</v>
       </c>
       <c r="K16" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L16" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6505</v>
+        <v>1.1301</v>
       </c>
       <c r="N16" t="n">
-        <v>184</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.828</v>
+        <v>1.871</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1924</v>
+        <v>0.197</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2079</v>
+        <v>0.2465</v>
       </c>
       <c r="E17" t="n">
-        <v>1.828</v>
+        <v>1.871</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4738</v>
+        <v>0.4755</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6458</v>
+        <v>1.3955</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2676</v>
+        <v>0.4755</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7645</v>
+        <v>0.267</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6458</v>
+        <v>1.3955</v>
       </c>
       <c r="K17" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L17" t="n">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1187</v>
+        <v>1.6625</v>
       </c>
       <c r="N17" t="n">
-        <v>95</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7765</v>
+        <v>1.8652</v>
       </c>
       <c r="C18" t="n">
-        <v>0.187</v>
+        <v>0.1963</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1845</v>
+        <v>0.2439</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7765</v>
+        <v>1.8652</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4016</v>
+        <v>2.4828</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6251</v>
+        <v>-0.6176</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0297</v>
+        <v>2.8791</v>
       </c>
       <c r="I18" t="n">
-        <v>1.636</v>
+        <v>1.6165</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6251</v>
+        <v>-0.6176</v>
       </c>
       <c r="K18" t="n">
         <v>51</v>
@@ -1265,7 +1265,7 @@
         <v>44</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0109</v>
+        <v>0.9989</v>
       </c>
       <c r="N18" t="n">
         <v>95</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7214</v>
+        <v>1.6325</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1812</v>
+        <v>0.1719</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1594</v>
+        <v>0.1379</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7214</v>
+        <v>1.6325</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7214</v>
+        <v>1.6325</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7214</v>
+        <v>1.6325</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7658</v>
+        <v>1.6762</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7658</v>
+        <v>1.6762</v>
       </c>
       <c r="N19" t="n">
         <v>162</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>disco doplan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4245</v>
+        <v>1.4051</v>
       </c>
       <c r="C20" t="n">
-        <v>0.15</v>
+        <v>0.1479</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0243</v>
+        <v>0.0343</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4245</v>
+        <v>1.4051</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4245</v>
+        <v>2.2295</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.8244</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4245</v>
+        <v>2.2295</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4612</v>
+        <v>1.2518</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.8244</v>
       </c>
       <c r="K20" t="n">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4612</v>
+        <v>0.4274</v>
       </c>
       <c r="N20" t="n">
-        <v>162</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4223</v>
+        <v>1.3853</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1497</v>
+        <v>0.1458</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0233</v>
+        <v>0.0253</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4223</v>
+        <v>1.3853</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4223</v>
+        <v>1.3853</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
+        <v>1.3853</v>
+      </c>
+      <c r="I21" t="n">
         <v>1.4223</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.459</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.459</v>
+        <v>1.4223</v>
       </c>
       <c r="N21" t="n">
         <v>162</v>
@@ -1412,81 +1412,81 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>freddieb</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3825</v>
+        <v>1.3536</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1455</v>
+        <v>0.1425</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0051</v>
+        <v>0.0108</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3825</v>
+        <v>1.3536</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7358</v>
+        <v>1.3536</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3533</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7358</v>
+        <v>1.3536</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9373</v>
+        <v>1.3897</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3533</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="L22" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5840000000000001</v>
+        <v>1.3897</v>
       </c>
       <c r="N22" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>disco doplan</t>
+          <t>freddieb</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3766</v>
+        <v>1.2237</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1449</v>
+        <v>0.1288</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0025</v>
+        <v>-0.0483</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3766</v>
+        <v>1.2237</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2185</v>
+        <v>1.5556</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8419</v>
+        <v>-0.3319</v>
       </c>
       <c r="H23" t="n">
-        <v>2.4256</v>
+        <v>1.5556</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3098</v>
+        <v>0.8734</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8419</v>
+        <v>-0.3319</v>
       </c>
       <c r="K23" t="n">
         <v>51</v>
@@ -1495,7 +1495,7 @@
         <v>44</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4679000000000001</v>
+        <v>0.5415</v>
       </c>
       <c r="N23" t="n">
         <v>95</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6062</v>
+        <v>0.5018</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0638</v>
+        <v>0.0528</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3482</v>
+        <v>-0.3772</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6062</v>
+        <v>0.5018</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6062</v>
+        <v>0.5018</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6062</v>
+        <v>0.5018</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6062</v>
+        <v>0.5018</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6062</v>
+        <v>0.5018</v>
       </c>
       <c r="N24" t="n">
         <v>92</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2352</v>
+        <v>0.2889</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0248</v>
+        <v>0.0304</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5171</v>
+        <v>-0.4742</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2352</v>
+        <v>0.2889</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2352</v>
+        <v>0.2889</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2352</v>
+        <v>0.2889</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2352</v>
+        <v>0.2889</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2352</v>
+        <v>0.2889</v>
       </c>
       <c r="N25" t="n">
         <v>83</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2269</v>
+        <v>0.1672</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0239</v>
+        <v>0.0176</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5209</v>
+        <v>-0.5296</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2269</v>
+        <v>0.1672</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2269</v>
+        <v>0.1672</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2269</v>
+        <v>0.1672</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2269</v>
+        <v>0.1672</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2269</v>
+        <v>0.1672</v>
       </c>
       <c r="N26" t="n">
         <v>83</v>
@@ -1642,32 +1642,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AZK</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1515</v>
+        <v>0.0866</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0159</v>
+        <v>0.0091</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5552</v>
+        <v>-0.5663</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1515</v>
+        <v>0.0866</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1515</v>
+        <v>0.0866</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1515</v>
+        <v>0.0866</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1515</v>
+        <v>0.0866</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1515</v>
+        <v>0.0866</v>
       </c>
       <c r="N27" t="n">
         <v>92</v>
@@ -1688,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>AZK</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1491</v>
+        <v>0.0837</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0157</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5563</v>
+        <v>-0.5677</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1491</v>
+        <v>0.0837</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1491</v>
+        <v>0.0837</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1491</v>
+        <v>0.0837</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1491</v>
+        <v>0.0837</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1491</v>
+        <v>0.0837</v>
       </c>
       <c r="N28" t="n">
         <v>92</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0074</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5815</v>
+        <v>-0.5739</v>
       </c>
       <c r="E29" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>92</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0362</v>
+        <v>0.0186</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0038</v>
+        <v>0.002</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6077</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0362</v>
+        <v>0.0186</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0362</v>
+        <v>0.0186</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0362</v>
+        <v>0.0186</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0362</v>
+        <v>0.0186</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0362</v>
+        <v>0.0186</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pollo</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0969</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0102</v>
+        <v>-0.0072</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6683</v>
+        <v>-0.637</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0969</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0969</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0969</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0969</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0969</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Pollo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1027</v>
+        <v>-0.1252</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0108</v>
+        <v>-0.0132</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.671</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1027</v>
+        <v>-0.1252</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1027</v>
+        <v>-0.1252</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1027</v>
+        <v>-0.1252</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1027</v>
+        <v>-0.1252</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1027</v>
+        <v>-0.1252</v>
       </c>
       <c r="N32" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2778</v>
+        <v>-0.2542</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0292</v>
+        <v>-0.0268</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7507</v>
+        <v>-0.7216</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2778</v>
+        <v>-0.2542</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1161</v>
+        <v>0.1154</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.3939</v>
+        <v>-0.3696</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1161</v>
+        <v>0.1154</v>
       </c>
       <c r="I33" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0648</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.3939</v>
+        <v>-0.3696</v>
       </c>
       <c r="K33" t="n">
         <v>51</v>
@@ -1955,7 +1955,7 @@
         <v>44</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3311999999999999</v>
+        <v>-0.3048</v>
       </c>
       <c r="N33" t="n">
         <v>95</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.349</v>
+        <v>-0.2554</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0367</v>
+        <v>-0.0269</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7831</v>
+        <v>-0.7221</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.349</v>
+        <v>-0.2554</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4982</v>
+        <v>-0.3744</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1492</v>
+        <v>0.119</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4982</v>
+        <v>-0.3744</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.269</v>
+        <v>-0.2102</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1492</v>
+        <v>0.119</v>
       </c>
       <c r="K34" t="n">
         <v>149</v>
@@ -2001,7 +2001,7 @@
         <v>77</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1198</v>
+        <v>-0.0912</v>
       </c>
       <c r="N34" t="n">
         <v>226</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4507</v>
+        <v>-0.3928</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0474</v>
+        <v>-0.0413</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8294</v>
+        <v>-0.7847</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4507</v>
+        <v>-0.3928</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4507</v>
+        <v>-0.3928</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4507</v>
+        <v>-0.3928</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4507</v>
+        <v>-0.3928</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4507</v>
+        <v>-0.3928</v>
       </c>
       <c r="N35" t="n">
         <v>70</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.6237</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0638</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9002</v>
+        <v>-0.8899</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.6237</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.6237</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.6237</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.6237</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.6237</v>
       </c>
       <c r="N36" t="n">
         <v>70</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7847</v>
+        <v>-0.7929</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.0835</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-0.967</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7847</v>
+        <v>-0.7929</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7847</v>
+        <v>-0.7929</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7847</v>
+        <v>-0.7929</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7847</v>
+        <v>-0.7929</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7847</v>
+        <v>-0.7929</v>
       </c>
       <c r="N37" t="n">
         <v>83</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0191</v>
+        <v>-0.9519</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1073</v>
+        <v>-0.1002</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0881</v>
+        <v>-1.0394</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0191</v>
+        <v>-0.9519</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0191</v>
+        <v>-0.9519</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0191</v>
+        <v>-0.9519</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0454</v>
+        <v>-0.9772999999999999</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0454</v>
+        <v>-0.9772999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>162</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1841</v>
+        <v>-1.1643</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1246</v>
+        <v>-0.1226</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1632</v>
+        <v>-1.1362</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1841</v>
+        <v>-1.1643</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1841</v>
+        <v>-1.1643</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1841</v>
+        <v>-1.1643</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1841</v>
+        <v>-1.1643</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1841</v>
+        <v>-1.1643</v>
       </c>
       <c r="N39" t="n">
         <v>70</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2814</v>
+        <v>-1.2262</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1349</v>
+        <v>-0.1291</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2075</v>
+        <v>-1.1644</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2814</v>
+        <v>-1.2262</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2814</v>
+        <v>-0.7341</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.4921</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2814</v>
+        <v>-0.7341</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2814</v>
+        <v>-0.4122</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.4921</v>
       </c>
       <c r="K40" t="n">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2814</v>
+        <v>-0.9043</v>
       </c>
       <c r="N40" t="n">
-        <v>70</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4963</v>
+        <v>-1.2585</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1575</v>
+        <v>-0.1325</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3053</v>
+        <v>-1.1791</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4963</v>
+        <v>-1.2585</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-1.2585</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5291</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-1.2585</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5223</v>
+        <v>-1.2585</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5291</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>149</v>
+        <v>70</v>
       </c>
       <c r="L41" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.0514</v>
+        <v>-1.2585</v>
       </c>
       <c r="N41" t="n">
-        <v>226</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.36</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8716</v>
+        <v>0.8524</v>
       </c>
       <c r="J2" t="n">
-        <v>24.4048</v>
+        <v>23.8672</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.28</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7116</v>
+        <v>0.6825</v>
       </c>
       <c r="J3" t="n">
-        <v>19.9248</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.608</v>
+        <v>0.5753</v>
       </c>
       <c r="J4" t="n">
-        <v>17.024</v>
+        <v>16.1084</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.08</v>
       </c>
       <c r="I5" t="n">
-        <v>0.256</v>
+        <v>0.2251</v>
       </c>
       <c r="J5" t="n">
-        <v>7.168</v>
+        <v>6.3028</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.07</v>
       </c>
       <c r="I6" t="n">
-        <v>0.228</v>
+        <v>0.1984</v>
       </c>
       <c r="J6" t="n">
-        <v>6.384</v>
+        <v>5.5552</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5065</v>
+        <v>0.4524</v>
       </c>
       <c r="J7" t="n">
-        <v>14.182</v>
+        <v>12.6672</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1594</v>
+        <v>-0.1417</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.4632</v>
+        <v>-3.9676</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.84</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2004</v>
+        <v>-0.1813</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.6112</v>
+        <v>-5.0764</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3168</v>
+        <v>-0.2996</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.8704</v>
+        <v>-8.3888</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3353</v>
+        <v>-0.3192</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.388400000000001</v>
+        <v>-8.9376</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.41</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9825</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>24.5625</v>
+        <v>24.3075</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.68</v>
+        <v>0.6474</v>
       </c>
       <c r="J13" t="n">
-        <v>17</v>
+        <v>16.185</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.23</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6163</v>
+        <v>0.5812</v>
       </c>
       <c r="J14" t="n">
-        <v>15.4075</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.07</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2367</v>
+        <v>0.2058</v>
       </c>
       <c r="J15" t="n">
-        <v>5.9175</v>
+        <v>5.145</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.79</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.64</v>
+        <v>-0.6058</v>
       </c>
       <c r="J16" t="n">
-        <v>-16</v>
+        <v>-15.145</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.26</v>
       </c>
       <c r="I17" t="n">
-        <v>0.535</v>
+        <v>0.4758</v>
       </c>
       <c r="J17" t="n">
-        <v>13.375</v>
+        <v>11.895</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4351</v>
+        <v>0.3776</v>
       </c>
       <c r="J18" t="n">
-        <v>10.8775</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2921</v>
+        <v>0.2421</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3025</v>
+        <v>6.0525</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.72</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3286</v>
+        <v>-0.3124</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.215</v>
+        <v>-7.81</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.67</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3745</v>
+        <v>-0.3618</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.362500000000001</v>
+        <v>-9.045</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0557</v>
+        <v>-0.0396</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.114</v>
+        <v>-0.792</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.67</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3422</v>
+        <v>-0.3295</v>
       </c>
       <c r="J23" t="n">
-        <v>-6.844</v>
+        <v>-6.59</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.66</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.351</v>
+        <v>-0.3384</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.02</v>
+        <v>-6.768</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3598</v>
+        <v>-0.3474</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.196</v>
+        <v>-6.948</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.51</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4834</v>
+        <v>-0.4798</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.667999999999999</v>
+        <v>-9.596</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.76</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2488</v>
+        <v>1.2481</v>
       </c>
       <c r="J27" t="n">
-        <v>24.976</v>
+        <v>24.962</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.39</v>
       </c>
       <c r="I28" t="n">
-        <v>0.777</v>
+        <v>0.7685</v>
       </c>
       <c r="J28" t="n">
-        <v>15.54</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.36</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7355</v>
+        <v>0.728</v>
       </c>
       <c r="J29" t="n">
-        <v>14.71</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.35</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7215</v>
+        <v>0.7143</v>
       </c>
       <c r="J30" t="n">
-        <v>14.43</v>
+        <v>14.286</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.28</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6194</v>
+        <v>0.6153</v>
       </c>
       <c r="J31" t="n">
-        <v>12.388</v>
+        <v>12.306</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>0.98</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0111</v>
+        <v>-0.0024</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2664</v>
+        <v>-0.0576</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.96</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0429</v>
+        <v>-0.0312</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.0296</v>
+        <v>-0.7488</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.74</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.286</v>
+        <v>-0.2701</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.864</v>
+        <v>-6.4824</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.66</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3585</v>
+        <v>-0.3446</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.603999999999999</v>
+        <v>-8.2704</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.42</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5694</v>
+        <v>-0.578</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.6656</v>
+        <v>-13.872</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.77</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2857</v>
+        <v>1.2876</v>
       </c>
       <c r="J37" t="n">
-        <v>30.8568</v>
+        <v>30.9024</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.38</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7728</v>
+        <v>0.7603</v>
       </c>
       <c r="J38" t="n">
-        <v>18.5472</v>
+        <v>18.2472</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.28</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6312</v>
+        <v>0.6236</v>
       </c>
       <c r="J39" t="n">
-        <v>15.1488</v>
+        <v>14.9664</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.08</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2388</v>
+        <v>0.2086</v>
       </c>
       <c r="J40" t="n">
-        <v>5.7312</v>
+        <v>5.0064</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.03</v>
       </c>
       <c r="I41" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="J41" t="n">
-        <v>2.064</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.11</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2346</v>
+        <v>0.22</v>
       </c>
       <c r="J42" t="n">
-        <v>6.8034</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0907</v>
+        <v>-0.077</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.6303</v>
+        <v>-2.233</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.9</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1385</v>
+        <v>-0.1215</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.0165</v>
+        <v>-3.5235</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.82</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2216</v>
+        <v>-0.202</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.4264</v>
+        <v>-5.858</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.65</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3822</v>
+        <v>-0.3694</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.0838</v>
+        <v>-10.7126</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.37</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4785</v>
+        <v>0.4247</v>
       </c>
       <c r="J47" t="n">
-        <v>13.8765</v>
+        <v>12.3163</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.3</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4151</v>
+        <v>0.3523</v>
       </c>
       <c r="J48" t="n">
-        <v>12.0379</v>
+        <v>10.2167</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.24</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3474</v>
+        <v>0.2895</v>
       </c>
       <c r="J49" t="n">
-        <v>10.0746</v>
+        <v>8.3955</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0126</v>
+        <v>-0.0101</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.3654</v>
+        <v>-0.2929</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.97</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0576</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.0851</v>
+        <v>-1.6704</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7195</v>
+        <v>0.7046</v>
       </c>
       <c r="J52" t="n">
-        <v>19.4265</v>
+        <v>19.0242</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5982</v>
+        <v>0.5876</v>
       </c>
       <c r="J53" t="n">
-        <v>16.1514</v>
+        <v>15.8652</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.2</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5192</v>
+        <v>0.5087</v>
       </c>
       <c r="J54" t="n">
-        <v>14.0184</v>
+        <v>13.7349</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.11</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3397</v>
+        <v>0.3056</v>
       </c>
       <c r="J55" t="n">
-        <v>9.171900000000001</v>
+        <v>8.251200000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.99</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0891</v>
+        <v>-0.0682</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.4057</v>
+        <v>-1.8414</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.17</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3892</v>
+        <v>0.3335</v>
       </c>
       <c r="J57" t="n">
-        <v>10.5084</v>
+        <v>9.0045</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.09</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2387</v>
+        <v>0.1931</v>
       </c>
       <c r="J58" t="n">
-        <v>6.4449</v>
+        <v>5.2137</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.93</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.109</v>
+        <v>-0.0919</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.943</v>
+        <v>-2.4813</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.88</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1665</v>
+        <v>-0.1465</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.4955</v>
+        <v>-3.9555</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.77</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2788</v>
+        <v>-0.2598</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.5276</v>
+        <v>-7.0146</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.57</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0153</v>
+        <v>1.0052</v>
       </c>
       <c r="J62" t="n">
-        <v>21.3213</v>
+        <v>21.1092</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.48</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8982</v>
+        <v>0.8871</v>
       </c>
       <c r="J63" t="n">
-        <v>18.8622</v>
+        <v>18.6291</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.39</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7791</v>
+        <v>0.7695</v>
       </c>
       <c r="J64" t="n">
-        <v>16.3611</v>
+        <v>16.1595</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.38</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.7564</v>
       </c>
       <c r="J65" t="n">
-        <v>16.0776</v>
+        <v>15.8844</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.17</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4455</v>
+        <v>0.4194</v>
       </c>
       <c r="J66" t="n">
-        <v>9.355499999999999</v>
+        <v>8.807399999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.05</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2142</v>
+        <v>0.1806</v>
       </c>
       <c r="J67" t="n">
-        <v>4.4982</v>
+        <v>3.7926</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.87</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1569</v>
+        <v>-0.1414</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.2949</v>
+        <v>-2.9694</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.72</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3045</v>
+        <v>-0.2886</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.3945</v>
+        <v>-6.0606</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.67</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.35</v>
+        <v>-0.3355</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.35</v>
+        <v>-7.0455</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.47</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5268</v>
+        <v>-0.529</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.0628</v>
+        <v>-11.109</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.08</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2979</v>
+        <v>0.2622</v>
       </c>
       <c r="J72" t="n">
-        <v>6.5538</v>
+        <v>5.7684</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.91</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1044</v>
+        <v>-0.0892</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.2968</v>
+        <v>-1.9624</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.71</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3107</v>
+        <v>-0.2959</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.8354</v>
+        <v>-6.5098</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.57</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4357</v>
+        <v>-0.4273</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.5854</v>
+        <v>-9.400600000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.36</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6182</v>
+        <v>-0.6345</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.6004</v>
+        <v>-13.959</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.86</v>
       </c>
       <c r="I77" t="n">
-        <v>1.5135</v>
+        <v>1.5459</v>
       </c>
       <c r="J77" t="n">
-        <v>33.297</v>
+        <v>34.0098</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.83</v>
       </c>
       <c r="I78" t="n">
-        <v>1.4775</v>
+        <v>1.5074</v>
       </c>
       <c r="J78" t="n">
-        <v>32.505</v>
+        <v>33.1628</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5544</v>
+        <v>0.5276</v>
       </c>
       <c r="J79" t="n">
-        <v>12.1968</v>
+        <v>11.6072</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.19</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4882</v>
+        <v>0.4588</v>
       </c>
       <c r="J80" t="n">
-        <v>10.7404</v>
+        <v>10.0936</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.14</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3717</v>
+        <v>0.3394</v>
       </c>
       <c r="J81" t="n">
-        <v>8.1774</v>
+        <v>7.4668</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.92</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.0572</v>
+        <v>-0.0334</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.0296</v>
+        <v>-0.6012</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.58</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.411</v>
+        <v>-0.4032</v>
       </c>
       <c r="J83" t="n">
-        <v>-7.398</v>
+        <v>-7.2576</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.4282</v>
+        <v>-0.4211</v>
       </c>
       <c r="J84" t="n">
-        <v>-7.7076</v>
+        <v>-7.5798</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.51</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4719</v>
+        <v>-0.4676</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.494199999999999</v>
+        <v>-8.4168</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.45</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5256</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.444599999999999</v>
+        <v>-9.460800000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>2.27</v>
       </c>
       <c r="I87" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J87" t="n">
-        <v>34.8696</v>
+        <v>35.6724</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.6</v>
       </c>
       <c r="I88" t="n">
-        <v>1.184</v>
+        <v>1.204</v>
       </c>
       <c r="J88" t="n">
-        <v>21.312</v>
+        <v>21.672</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.43</v>
       </c>
       <c r="I89" t="n">
-        <v>0.954</v>
+        <v>0.9575</v>
       </c>
       <c r="J89" t="n">
-        <v>17.172</v>
+        <v>17.235</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.29</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6873</v>
+        <v>0.6687</v>
       </c>
       <c r="J90" t="n">
-        <v>12.3714</v>
+        <v>12.0366</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.13</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3338</v>
+        <v>0.2995</v>
       </c>
       <c r="J91" t="n">
-        <v>6.0084</v>
+        <v>5.391</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2942</v>
+        <v>0.2818</v>
       </c>
       <c r="J92" t="n">
-        <v>7.355</v>
+        <v>7.045</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.13</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2381</v>
+        <v>0.223</v>
       </c>
       <c r="J93" t="n">
-        <v>5.9525</v>
+        <v>5.575</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.07</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1467</v>
+        <v>0.1307</v>
       </c>
       <c r="J94" t="n">
-        <v>3.6675</v>
+        <v>3.2675</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.91</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.138</v>
+        <v>-0.1185</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.45</v>
+        <v>-2.9625</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.87</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1828</v>
+        <v>-0.1622</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.57</v>
+        <v>-4.055</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.5578</v>
       </c>
       <c r="J97" t="n">
-        <v>15.7375</v>
+        <v>13.945</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.41</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5356</v>
+        <v>0.466</v>
       </c>
       <c r="J98" t="n">
-        <v>13.39</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.14</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2269</v>
+        <v>0.1824</v>
       </c>
       <c r="J99" t="n">
-        <v>5.6725</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.93</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1257</v>
+        <v>-0.1072</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.1425</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.89</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1727</v>
+        <v>-0.1529</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.3175</v>
+        <v>-3.8225</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.35</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8653</v>
+        <v>0.8444</v>
       </c>
       <c r="J102" t="n">
-        <v>25.0937</v>
+        <v>24.4876</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.25</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6597</v>
+        <v>0.6261</v>
       </c>
       <c r="J103" t="n">
-        <v>19.1313</v>
+        <v>18.1569</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.15</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4396</v>
+        <v>0.4024</v>
       </c>
       <c r="J104" t="n">
-        <v>12.7484</v>
+        <v>11.6696</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1784</v>
+        <v>0.1513</v>
       </c>
       <c r="J105" t="n">
-        <v>5.1736</v>
+        <v>4.3877</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2584</v>
+        <v>-0.2196</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.4936</v>
+        <v>-6.3684</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.01</v>
       </c>
       <c r="I107" t="n">
-        <v>0.0553</v>
+        <v>0.0376</v>
       </c>
       <c r="J107" t="n">
-        <v>1.6037</v>
+        <v>1.0904</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0553</v>
+        <v>0.0376</v>
       </c>
       <c r="J108" t="n">
-        <v>1.6037</v>
+        <v>1.0904</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.95</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.081</v>
+        <v>-0.0675</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.349</v>
+        <v>-1.9575</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.91</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1292</v>
+        <v>-0.1118</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.7468</v>
+        <v>-3.2422</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.72</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3216</v>
+        <v>-0.3047</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.3264</v>
+        <v>-8.8363</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.58</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2337</v>
+        <v>1.2523</v>
       </c>
       <c r="J112" t="n">
-        <v>37.011</v>
+        <v>37.569</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.19</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5341</v>
+        <v>0.4958</v>
       </c>
       <c r="J113" t="n">
-        <v>16.023</v>
+        <v>14.874</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.09</v>
       </c>
       <c r="I114" t="n">
-        <v>0.296</v>
+        <v>0.2612</v>
       </c>
       <c r="J114" t="n">
-        <v>8.880000000000001</v>
+        <v>7.836</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.91</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3389</v>
+        <v>-0.297</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.167</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5175</v>
+        <v>-0.4769</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.525</v>
+        <v>-14.307</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4812</v>
+        <v>0.4224</v>
       </c>
       <c r="J117" t="n">
-        <v>14.436</v>
+        <v>12.672</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.03</v>
       </c>
       <c r="I118" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0731</v>
       </c>
       <c r="J118" t="n">
-        <v>2.958</v>
+        <v>2.193</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.03</v>
       </c>
       <c r="I119" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0731</v>
       </c>
       <c r="J119" t="n">
-        <v>2.958</v>
+        <v>2.193</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.93</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1125</v>
+        <v>-0.0945</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.375</v>
+        <v>-2.835</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.213</v>
+        <v>-0.1924</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.39</v>
+        <v>-5.772</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.02</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1803</v>
+        <v>0.167</v>
       </c>
       <c r="J122" t="n">
-        <v>3.7863</v>
+        <v>3.507</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.79</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2256</v>
+        <v>-0.2109</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.7376</v>
+        <v>-4.4289</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.59</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.4097</v>
+        <v>-0.4001</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.6037</v>
+        <v>-8.402100000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.54</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4538</v>
+        <v>-0.4473</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.5298</v>
+        <v>-9.3933</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.37</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6027</v>
+        <v>-0.6153</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.6567</v>
+        <v>-12.9213</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.8</v>
       </c>
       <c r="I127" t="n">
-        <v>1.4264</v>
+        <v>1.4543</v>
       </c>
       <c r="J127" t="n">
-        <v>29.9544</v>
+        <v>30.5403</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.73</v>
       </c>
       <c r="I128" t="n">
-        <v>1.3426</v>
+        <v>1.3667</v>
       </c>
       <c r="J128" t="n">
-        <v>28.1946</v>
+        <v>28.7007</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.71</v>
       </c>
       <c r="I129" t="n">
-        <v>1.3184</v>
+        <v>1.3417</v>
       </c>
       <c r="J129" t="n">
-        <v>27.6864</v>
+        <v>28.1757</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.47</v>
       </c>
       <c r="I130" t="n">
-        <v>1.0179</v>
+        <v>1.0299</v>
       </c>
       <c r="J130" t="n">
-        <v>21.3759</v>
+        <v>21.6279</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.0856</v>
+        <v>-0.0872</v>
       </c>
       <c r="J131" t="n">
-        <v>-1.7976</v>
+        <v>-1.8312</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I132" t="n">
-        <v>0.0268</v>
+        <v>0.0629</v>
       </c>
       <c r="J132" t="n">
-        <v>0.5092</v>
+        <v>1.1951</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.9</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0842</v>
+        <v>-0.0614</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.5998</v>
+        <v>-1.1666</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.44</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="J134" t="n">
-        <v>-10.1422</v>
+        <v>-10.1802</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.42</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5515</v>
+        <v>-0.5557</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.4785</v>
+        <v>-10.5583</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.3</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6572</v>
+        <v>-0.6788</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.4868</v>
+        <v>-12.8972</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.44</v>
       </c>
       <c r="I137" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J137" t="n">
-        <v>36.8068</v>
+        <v>37.6542</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.67</v>
       </c>
       <c r="I138" t="n">
-        <v>1.261</v>
+        <v>1.2856</v>
       </c>
       <c r="J138" t="n">
-        <v>23.959</v>
+        <v>24.4264</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.63</v>
       </c>
       <c r="I139" t="n">
-        <v>1.2141</v>
+        <v>1.2377</v>
       </c>
       <c r="J139" t="n">
-        <v>23.0679</v>
+        <v>23.5163</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.32</v>
       </c>
       <c r="I140" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7197</v>
       </c>
       <c r="J140" t="n">
-        <v>13.9536</v>
+        <v>13.6743</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.15</v>
       </c>
       <c r="I141" t="n">
-        <v>0.3694</v>
+        <v>0.334</v>
       </c>
       <c r="J141" t="n">
-        <v>7.0186</v>
+        <v>6.346</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.07</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2327</v>
+        <v>0.191</v>
       </c>
       <c r="J142" t="n">
-        <v>5.5848</v>
+        <v>4.584</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.01</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0771</v>
+        <v>0.0577</v>
       </c>
       <c r="J143" t="n">
-        <v>1.8504</v>
+        <v>1.3848</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.79</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2461</v>
+        <v>-0.2276</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.9064</v>
+        <v>-5.4624</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3765</v>
+        <v>-0.3631</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.036</v>
+        <v>-8.714399999999999</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.63</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3945</v>
+        <v>-0.3825</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.468</v>
+        <v>-9.18</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.83</v>
       </c>
       <c r="I147" t="n">
-        <v>1.4919</v>
+        <v>1.5229</v>
       </c>
       <c r="J147" t="n">
-        <v>35.8056</v>
+        <v>36.5496</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.4</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9184</v>
+        <v>0.9105</v>
       </c>
       <c r="J148" t="n">
-        <v>22.0416</v>
+        <v>21.852</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.39</v>
       </c>
       <c r="I149" t="n">
-        <v>0.9004</v>
+        <v>0.891</v>
       </c>
       <c r="J149" t="n">
-        <v>21.6096</v>
+        <v>21.384</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.39</v>
       </c>
       <c r="I150" t="n">
-        <v>0.9004</v>
+        <v>0.891</v>
       </c>
       <c r="J150" t="n">
-        <v>21.6096</v>
+        <v>21.384</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.87</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4854</v>
+        <v>-0.4506</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.6496</v>
+        <v>-10.8144</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.22</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4619</v>
+        <v>0.4035</v>
       </c>
       <c r="J152" t="n">
-        <v>12.4713</v>
+        <v>10.8945</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2087</v>
+        <v>0.1673</v>
       </c>
       <c r="J153" t="n">
-        <v>5.6349</v>
+        <v>4.5171</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.03</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0975</v>
+        <v>0.0726</v>
       </c>
       <c r="J154" t="n">
-        <v>2.6325</v>
+        <v>1.9602</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1009</v>
+        <v>-0.0837</v>
       </c>
       <c r="J155" t="n">
-        <v>-2.7243</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2036</v>
+        <v>-0.183</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.4972</v>
+        <v>-4.941</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.29</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7467</v>
+        <v>0.717</v>
       </c>
       <c r="J157" t="n">
-        <v>20.1609</v>
+        <v>19.359</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.28</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7259</v>
+        <v>0.695</v>
       </c>
       <c r="J158" t="n">
-        <v>19.5993</v>
+        <v>18.765</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3705</v>
+        <v>0.3337</v>
       </c>
       <c r="J159" t="n">
-        <v>10.0035</v>
+        <v>9.0099</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.12</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3705</v>
+        <v>0.3337</v>
       </c>
       <c r="J160" t="n">
-        <v>10.0035</v>
+        <v>9.0099</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4708</v>
+        <v>-0.4292</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.7116</v>
+        <v>-11.5884</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.52</v>
       </c>
       <c r="I162" t="n">
-        <v>1.1171</v>
+        <v>1.1294</v>
       </c>
       <c r="J162" t="n">
-        <v>26.8104</v>
+        <v>27.1056</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.35</v>
       </c>
       <c r="I163" t="n">
-        <v>0.839</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>20.136</v>
+        <v>19.6824</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.34</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8196</v>
+        <v>0.7996</v>
       </c>
       <c r="J164" t="n">
-        <v>19.6704</v>
+        <v>19.1904</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.19</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5145</v>
+        <v>0.4832</v>
       </c>
       <c r="J165" t="n">
-        <v>12.348</v>
+        <v>11.5968</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.96</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2177</v>
+        <v>-0.1845</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.2248</v>
+        <v>-4.428</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.15</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3804</v>
+        <v>0.3278</v>
       </c>
       <c r="J167" t="n">
-        <v>9.1296</v>
+        <v>7.8672</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2625</v>
+        <v>0.2162</v>
       </c>
       <c r="J168" t="n">
-        <v>6.3</v>
+        <v>5.1888</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1697</v>
+        <v>-0.1516</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.0728</v>
+        <v>-3.6384</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.66</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3719</v>
+        <v>-0.3582</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.925599999999999</v>
+        <v>-8.5968</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.59</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4344</v>
+        <v>-0.4265</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.4256</v>
+        <v>-10.236</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.19</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4415</v>
+        <v>0.3857</v>
       </c>
       <c r="J172" t="n">
-        <v>10.596</v>
+        <v>9.2568</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.15</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3692</v>
+        <v>0.3154</v>
       </c>
       <c r="J173" t="n">
-        <v>8.860799999999999</v>
+        <v>7.5696</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.93</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1054</v>
+        <v>-0.09</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.5296</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.64</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3936</v>
+        <v>-0.3819</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.446400000000001</v>
+        <v>-9.1656</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4025</v>
+        <v>-0.3917</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.66</v>
+        <v>-9.4008</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2019</v>
+        <v>1.2168</v>
       </c>
       <c r="J177" t="n">
-        <v>28.8456</v>
+        <v>29.2032</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.55</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1619</v>
+        <v>1.1754</v>
       </c>
       <c r="J178" t="n">
-        <v>27.8856</v>
+        <v>28.2096</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.23</v>
       </c>
       <c r="I179" t="n">
-        <v>0.6039</v>
+        <v>0.5734</v>
       </c>
       <c r="J179" t="n">
-        <v>14.4936</v>
+        <v>13.7616</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.12</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3535</v>
+        <v>0.3209</v>
       </c>
       <c r="J180" t="n">
-        <v>8.484</v>
+        <v>7.7016</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.76</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.723</v>
+        <v>-0.6973</v>
       </c>
       <c r="J181" t="n">
-        <v>-17.352</v>
+        <v>-16.7352</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I182" t="n">
-        <v>0.0107</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="J182" t="n">
-        <v>0.2033</v>
+        <v>1.4307</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.52</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.4521</v>
+        <v>-0.4493</v>
       </c>
       <c r="J183" t="n">
-        <v>-8.5899</v>
+        <v>-8.5367</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.47</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.4947</v>
+        <v>-0.4937</v>
       </c>
       <c r="J184" t="n">
-        <v>-9.3993</v>
+        <v>-9.3803</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.47</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4947</v>
+        <v>-0.4937</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.3993</v>
+        <v>-9.3803</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.23</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7101</v>
+        <v>-0.741</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.4919</v>
+        <v>-14.079</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.17</v>
       </c>
       <c r="I187" t="n">
-        <v>1.8449</v>
+        <v>1.9064</v>
       </c>
       <c r="J187" t="n">
-        <v>35.0531</v>
+        <v>36.2216</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.96</v>
       </c>
       <c r="I188" t="n">
-        <v>1.6071</v>
+        <v>1.6471</v>
       </c>
       <c r="J188" t="n">
-        <v>30.5349</v>
+        <v>31.2949</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.41</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9137</v>
+        <v>0.9136</v>
       </c>
       <c r="J189" t="n">
-        <v>17.3603</v>
+        <v>17.3584</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.29</v>
       </c>
       <c r="I190" t="n">
-        <v>0.6819</v>
+        <v>0.6632</v>
       </c>
       <c r="J190" t="n">
-        <v>12.9561</v>
+        <v>12.6008</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.09</v>
       </c>
       <c r="I191" t="n">
-        <v>0.226</v>
+        <v>0.1904</v>
       </c>
       <c r="J191" t="n">
-        <v>4.294</v>
+        <v>3.6176</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7857</v>
+        <v>0.7621</v>
       </c>
       <c r="J192" t="n">
-        <v>21.2139</v>
+        <v>20.5767</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.28</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7059</v>
+        <v>0.6784</v>
       </c>
       <c r="J193" t="n">
-        <v>19.0593</v>
+        <v>18.3168</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.22</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5838</v>
+        <v>0.5525</v>
       </c>
       <c r="J194" t="n">
-        <v>15.7626</v>
+        <v>14.9175</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.21</v>
       </c>
       <c r="I195" t="n">
-        <v>0.5626</v>
+        <v>0.5308</v>
       </c>
       <c r="J195" t="n">
-        <v>15.1902</v>
+        <v>14.3316</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.17</v>
       </c>
       <c r="I196" t="n">
-        <v>0.4741</v>
+        <v>0.4411</v>
       </c>
       <c r="J196" t="n">
-        <v>12.8007</v>
+        <v>11.9097</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.387</v>
+        <v>0.3325</v>
       </c>
       <c r="J197" t="n">
-        <v>10.449</v>
+        <v>8.977499999999999</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.07</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2098</v>
+        <v>0.1674</v>
       </c>
       <c r="J198" t="n">
-        <v>5.6646</v>
+        <v>4.5198</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.97</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.052</v>
+        <v>-0.0419</v>
       </c>
       <c r="J199" t="n">
-        <v>-1.404</v>
+        <v>-1.1313</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.92</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1174</v>
+        <v>-0.101</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.1698</v>
+        <v>-2.727</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.43</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.575</v>
+        <v>-0.5867</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.525</v>
+        <v>-15.8409</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.71</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3651</v>
+        <v>1.3884</v>
       </c>
       <c r="J202" t="n">
-        <v>40.953</v>
+        <v>41.652</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.35</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8387</v>
+        <v>0.8198</v>
       </c>
       <c r="J203" t="n">
-        <v>25.161</v>
+        <v>24.594</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.27</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6826</v>
+        <v>0.6559</v>
       </c>
       <c r="J204" t="n">
-        <v>20.478</v>
+        <v>19.677</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.21</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5581</v>
+        <v>0.5278</v>
       </c>
       <c r="J205" t="n">
-        <v>16.743</v>
+        <v>15.834</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.83</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5674</v>
+        <v>-0.5326</v>
       </c>
       <c r="J206" t="n">
-        <v>-17.022</v>
+        <v>-15.978</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.14</v>
       </c>
       <c r="I207" t="n">
-        <v>0.346</v>
+        <v>0.2929</v>
       </c>
       <c r="J207" t="n">
-        <v>10.38</v>
+        <v>8.787000000000001</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.96</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0678</v>
+        <v>-0.0556</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.034</v>
+        <v>-1.668</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.91</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1295</v>
+        <v>-0.1119</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.885</v>
+        <v>-3.357</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.86</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1841</v>
+        <v>-0.1643</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.523</v>
+        <v>-4.929</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.75</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2938</v>
+        <v>-0.2754</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.814</v>
+        <v>-8.262</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.37</v>
       </c>
       <c r="I212" t="n">
-        <v>0.924</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="J212" t="n">
-        <v>37.884</v>
+        <v>37.2608</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.18</v>
       </c>
       <c r="I213" t="n">
-        <v>0.519</v>
+        <v>0.4789</v>
       </c>
       <c r="J213" t="n">
-        <v>21.279</v>
+        <v>19.6349</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1241</v>
+        <v>0.1011</v>
       </c>
       <c r="J214" t="n">
-        <v>5.0881</v>
+        <v>4.1451</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.98</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1138</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.6658</v>
+        <v>-3.5834</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.86</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4613</v>
+        <v>-0.4188</v>
       </c>
       <c r="J216" t="n">
-        <v>-18.9133</v>
+        <v>-17.1708</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.28</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5435</v>
+        <v>0.4839</v>
       </c>
       <c r="J217" t="n">
-        <v>22.2835</v>
+        <v>19.8399</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.21</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4316</v>
+        <v>0.375</v>
       </c>
       <c r="J218" t="n">
-        <v>17.6956</v>
+        <v>15.375</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3985</v>
+        <v>0.3434</v>
       </c>
       <c r="J219" t="n">
-        <v>16.3385</v>
+        <v>14.0794</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.02</v>
       </c>
       <c r="I220" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0468</v>
       </c>
       <c r="J220" t="n">
-        <v>2.6117</v>
+        <v>1.9188</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.77</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2899</v>
+        <v>-0.2721</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.8859</v>
+        <v>-11.1561</v>
       </c>
     </row>
   </sheetData>
